--- a/data/deidentified_clinical_consolidated.xlsx
+++ b/data/deidentified_clinical_consolidated.xlsx
@@ -14,18 +14,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="295">
   <si>
     <t>Anonymous_ID</t>
   </si>
   <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Age (Estimated)</t>
+  </si>
+  <si>
     <t>Gender</t>
   </si>
   <si>
-    <t>Age</t>
-  </si>
-  <si>
-    <t>Age (Estimated)</t>
+    <t>Time since diagnosis (Years)</t>
+  </si>
+  <si>
+    <t>Time since diagnosis (Years) (Estimated)</t>
   </si>
   <si>
     <t>Age of onset</t>
@@ -205,15 +211,12 @@
     <t>Cardiac problems description</t>
   </si>
   <si>
-    <t>Time since diagnosis (Years)</t>
-  </si>
-  <si>
-    <t>Time since diagnosis (Years) (Estimated)</t>
-  </si>
-  <si>
     <t>P001</t>
   </si>
   <si>
+    <t>P002</t>
+  </si>
+  <si>
     <t>P003</t>
   </si>
   <si>
@@ -223,12 +226,12 @@
     <t>P005</t>
   </si>
   <si>
-    <t>P006</t>
-  </si>
-  <si>
     <t>P007</t>
   </si>
   <si>
+    <t>P008</t>
+  </si>
+  <si>
     <t>P009</t>
   </si>
   <si>
@@ -238,9 +241,6 @@
     <t>P012</t>
   </si>
   <si>
-    <t>P013</t>
-  </si>
-  <si>
     <t>P014</t>
   </si>
   <si>
@@ -253,6 +253,9 @@
     <t>P017</t>
   </si>
   <si>
+    <t>P018</t>
+  </si>
+  <si>
     <t>P020</t>
   </si>
   <si>
@@ -262,7 +265,7 @@
     <t>P022</t>
   </si>
   <si>
-    <t>P023</t>
+    <t>P024</t>
   </si>
   <si>
     <t>P025</t>
@@ -304,289 +307,598 @@
     <t>P037</t>
   </si>
   <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>M</t>
+    <t>77 años (estimado)</t>
+  </si>
+  <si>
+    <t>51 años (estimado)</t>
+  </si>
+  <si>
+    <t>≈72 años (estimado)</t>
+  </si>
+  <si>
+    <t>62 años (estimado)</t>
+  </si>
+  <si>
+    <t>52 años</t>
+  </si>
+  <si>
+    <t>65 años (estimado)</t>
+  </si>
+  <si>
+    <t>47 años (estimado)</t>
+  </si>
+  <si>
+    <t>68 años (estimado)</t>
+  </si>
+  <si>
+    <t>Femenino</t>
+  </si>
+  <si>
+    <t>Masculino</t>
+  </si>
+  <si>
+    <t>Masculino (estimado)</t>
+  </si>
+  <si>
+    <t>≈10 años (estimado)</t>
+  </si>
+  <si>
+    <t>3 años (estimado)</t>
+  </si>
+  <si>
+    <t>11 años</t>
+  </si>
+  <si>
+    <t>1 año (estimado)</t>
+  </si>
+  <si>
+    <t>≈2,2 años (estimado)</t>
+  </si>
+  <si>
+    <t>6 años</t>
+  </si>
+  <si>
+    <t>8 años</t>
+  </si>
+  <si>
+    <t>3,3 años (estimado)</t>
+  </si>
+  <si>
+    <t>6 años (estimado)</t>
+  </si>
+  <si>
+    <t>≈67 años (estimado)</t>
+  </si>
+  <si>
+    <t>≈62 años (estimado)</t>
+  </si>
+  <si>
+    <t>51 años</t>
+  </si>
+  <si>
+    <t>61 años (estimado)</t>
+  </si>
+  <si>
+    <t>57 años (estimado)</t>
+  </si>
+  <si>
+    <t>56 años (estimado)</t>
+  </si>
+  <si>
+    <t>44 años (estimado)</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>Yes (father with Parkinson's disease)</t>
-  </si>
-  <si>
-    <t>Yes (father with Lewy body dementia)</t>
-  </si>
-  <si>
-    <t>Yes (cousin with Parkinson's disease)</t>
-  </si>
-  <si>
-    <t>Yes</t>
+    <t>Sí (padre con enfermedad de Parkinson)</t>
+  </si>
+  <si>
+    <t>No (estimado)</t>
+  </si>
+  <si>
+    <t>Sí (padre con demencia con cuerpos de Lewy)</t>
+  </si>
+  <si>
+    <t>Sí (primo con enfermedad de Parkinson)</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
   <si>
     <t>Sí (nº 0793)</t>
   </si>
   <si>
-    <t>Yes (study number 0450)</t>
-  </si>
-  <si>
-    <t>Yes (LargePD genetic study requested)</t>
-  </si>
-  <si>
-    <t>Yes (nº 0713)</t>
-  </si>
-  <si>
-    <t>PDgeneration study negative (no pathogenic variant identified)</t>
-  </si>
-  <si>
-    <t>Genetic study performed, result not reported</t>
-  </si>
-  <si>
-    <t>Not studied / no gene identified</t>
-  </si>
-  <si>
-    <t>No PD-related gene identified</t>
-  </si>
-  <si>
-    <t>Genetic study requested, result not available</t>
-  </si>
-  <si>
-    <t>Not performed / not recorded</t>
-  </si>
-  <si>
-    <t>No genetic variant associated with PD identified</t>
-  </si>
-  <si>
-    <t>Not identified (study performed, result pending)</t>
-  </si>
-  <si>
-    <t>Hypothyroidism, HTN</t>
-  </si>
-  <si>
-    <t>Chronic kidney failure, arterial hypertension, mixed polyneuropathy, bronchopneumonia</t>
-  </si>
-  <si>
-    <t>Insulin resistance, Gout</t>
-  </si>
-  <si>
-    <t>Ulcerative proctitis, bilateral inguinal hernia, deep vein thrombosis (DVT)</t>
-  </si>
-  <si>
-    <t>Hypertension, Diabetes Mellitus</t>
-  </si>
-  <si>
-    <t>HTN</t>
-  </si>
-  <si>
-    <t>Essential HTN</t>
-  </si>
-  <si>
-    <t>Arterial hypertension, right eye prosthesis</t>
-  </si>
-  <si>
-    <t>Hearing loss</t>
-  </si>
-  <si>
-    <t>Uterine cancer</t>
-  </si>
-  <si>
-    <t>HTN, Depression</t>
+    <t>Sí (número de estudio 0450)</t>
+  </si>
+  <si>
+    <t>Sí (estudio genético LargePD solicitado)</t>
+  </si>
+  <si>
+    <t>Sí (nº 0713)</t>
+  </si>
+  <si>
+    <t>Estudio PDgeneration negativo (sin variante patogénica identificada)</t>
+  </si>
+  <si>
+    <t>Estudio genético realizado, resultado no consignado</t>
+  </si>
+  <si>
+    <t>No estudiada / sin gen identificado (estimado)</t>
+  </si>
+  <si>
+    <t>No se ha identificado gen relacionado a EP (estimado)</t>
+  </si>
+  <si>
+    <t>Estudio genético solicitado, resultado no disponible</t>
+  </si>
+  <si>
+    <t>No realizada / no registrada</t>
+  </si>
+  <si>
+    <t>No se ha identificado variante genética asociada a EP</t>
+  </si>
+  <si>
+    <t>No se ha identificado (estudio realizado, resultado pendiente)</t>
+  </si>
+  <si>
+    <t>2 (estimado)</t>
+  </si>
+  <si>
+    <t>4 (estimado)</t>
+  </si>
+  <si>
+    <t>Estadio 2 (estimado)</t>
+  </si>
+  <si>
+    <t>1 (estimado)</t>
+  </si>
+  <si>
+    <t>3 (estimado)</t>
+  </si>
+  <si>
+    <t>80 % (estimado)</t>
+  </si>
+  <si>
+    <t>90% (estimado)</t>
+  </si>
+  <si>
+    <t>≈60 % (estimado)</t>
+  </si>
+  <si>
+    <t>90 % (estimado)</t>
+  </si>
+  <si>
+    <t>100% (estimado)</t>
+  </si>
+  <si>
+    <t>80% (estimado)</t>
+  </si>
+  <si>
+    <t>3 (moderados, estimado)</t>
+  </si>
+  <si>
+    <t>2 (leves) (estimado)</t>
+  </si>
+  <si>
+    <t>4 (marcados, estimado)</t>
+  </si>
+  <si>
+    <t>2/6 (leve-moderado, estimado)</t>
+  </si>
+  <si>
+    <t>1 (muy leves) (estimado)</t>
+  </si>
+  <si>
+    <t>1 (mínimos, estimado)</t>
+  </si>
+  <si>
+    <t>3 (moderados) (estimado)</t>
+  </si>
+  <si>
+    <t>2 (leves, estimado)</t>
+  </si>
+  <si>
+    <t>3 (leves a moderados) (estimado)</t>
+  </si>
+  <si>
+    <t>3 (limitaciones en actividades, estimado)</t>
+  </si>
+  <si>
+    <t>4 (moderada-grave, estimado)</t>
+  </si>
+  <si>
+    <t>1/6 (muy leve, estimado)</t>
+  </si>
+  <si>
+    <t>0 (estimado)</t>
+  </si>
+  <si>
+    <t>1 (mínima, estimado)</t>
+  </si>
+  <si>
+    <t>3 (limitaciones en actividades exigentes, estimado)</t>
+  </si>
+  <si>
+    <t>3 (moderadas, estimado)</t>
+  </si>
+  <si>
+    <t>2/6 (leve-moderadas, estimado)</t>
+  </si>
+  <si>
+    <t>3 (moderadas-graves, estimado)</t>
+  </si>
+  <si>
+    <t>3 (leves a moderadas, estimado)</t>
+  </si>
+  <si>
+    <t>0 (sin compromiso significativo, estimado)</t>
+  </si>
+  <si>
+    <t>0/6 (sin compromiso relevante, estimado)</t>
+  </si>
+  <si>
+    <t>1 (mínimo compromiso, estimado)</t>
+  </si>
+  <si>
+    <t>9/24 (estimado)</t>
+  </si>
+  <si>
+    <t>≈11/24 (estimado)</t>
+  </si>
+  <si>
+    <t>≈5/24 (estimado)</t>
+  </si>
+  <si>
+    <t>10 (estimado)</t>
+  </si>
+  <si>
+    <t>9 (estimado)</t>
+  </si>
+  <si>
+    <t>Hipotiroidismo, HTA</t>
+  </si>
+  <si>
+    <t>Cáncer uterino</t>
+  </si>
+  <si>
+    <t>Proctitis ulcerosa, hernia inguinal bilateral, TVP</t>
+  </si>
+  <si>
+    <t>HTA</t>
+  </si>
+  <si>
+    <t>Psoriasis</t>
+  </si>
+  <si>
+    <t>HTA, DM2</t>
+  </si>
+  <si>
+    <t>HTA, DM2, dislipidemia</t>
+  </si>
+  <si>
+    <t>Resistencia a la insulina, Gota</t>
+  </si>
+  <si>
+    <t>Ninguna</t>
+  </si>
+  <si>
+    <t>Hipoacusia</t>
+  </si>
+  <si>
+    <t>HTA, prótesis ocular derecha</t>
+  </si>
+  <si>
+    <t>Hipotiroidismo</t>
+  </si>
+  <si>
+    <t>TBC pulmonar</t>
   </si>
   <si>
     <t>HTA, dislipidemia, temblor esencial</t>
   </si>
   <si>
-    <t>HTN, T2DM, dyslipidemia</t>
-  </si>
-  <si>
-    <t>Hypothyroidism</t>
-  </si>
-  <si>
-    <t>HTN, Diabetes</t>
-  </si>
-  <si>
-    <t>Hypertension</t>
-  </si>
-  <si>
-    <t>Osteoarthritis</t>
-  </si>
-  <si>
-    <t>Spinal stenosis L4-L5, operated abdominal aortic aneurysm, right knee gonarthrosis with meniscopathy, possible cardiovascular / mild atherosclerotic disease, mild chronic kidney disease</t>
-  </si>
-  <si>
-    <t>Probable anxious-depressive disorder on SSRI treatment; snoring with occasional sleep apnea</t>
-  </si>
-  <si>
-    <t>Osteoporosis, cervical cancer (awaiting hysterectomy), operated abdominal hernia</t>
-  </si>
-  <si>
-    <t>Arterial hypertension, hypertriglyceridemia, type 2 diabetes mellitus</t>
-  </si>
-  <si>
-    <t>Autoimmune hypothyroidism; dyslipidemia; prediabetes; left middle fossa arachnoid cyst; sinus bradycardia under study; erectile dysfunction.</t>
-  </si>
-  <si>
-    <t>Dyslipidemia, panic attacks, depressive disorder, active smoking, chronic right shoulder pain, probable hypovitaminosis D</t>
-  </si>
-  <si>
-    <t>Arterial hypertension; spinal osteoarthritis with lumbar herniated nucleus pulposus (HNP); surgical history of umbilical hernia and right shoulder tendon rupture; anxious-depressive symptoms managed with escitalopram.</t>
-  </si>
-  <si>
-    <t>Dyslipidemia; probable reactive depressive disorder; chronic constipation; hyposmia; sialorrhea; sleep onset insomnia and fragmented sleep.</t>
-  </si>
-  <si>
-    <t>Fatty liver, metabolic syndrome, carpal tunnel syndrome, depressive/anxious disorder</t>
-  </si>
-  <si>
-    <t>HTN, dyslipidemia, BPH, Type 2 Diabetes Mellitus, chronic lower back pain due to foraminal stenosis L3-S1 and spondyloarthrosis, sleep apnea on CPAP treatment, decreased visual acuity.</t>
-  </si>
-  <si>
-    <t>Not recorded</t>
-  </si>
-  <si>
-    <t>Absent</t>
-  </si>
-  <si>
-    <t>Yes (T2DM)</t>
-  </si>
-  <si>
-    <t>Absent (prediabetes)</t>
-  </si>
-  <si>
-    <t>Present</t>
-  </si>
-  <si>
-    <t>Present (history)</t>
-  </si>
-  <si>
-    <t>Present (reactive, mild-moderate)</t>
-  </si>
-  <si>
-    <t>Absent (currently, on SSRI treatment)</t>
-  </si>
-  <si>
-    <t>Present (history of depressive disorder, apathetic/fluctuating mood)</t>
-  </si>
-  <si>
-    <t>Present (anxious-depressive symptoms)</t>
-  </si>
-  <si>
-    <t>Present (reactive / depressive symptoms)</t>
-  </si>
-  <si>
-    <t>Present (mild)</t>
-  </si>
-  <si>
-    <t>Present (urgency, urge incontinence, nocturia)</t>
-  </si>
-  <si>
-    <t>Present (previous nocturia, currently resolved)</t>
-  </si>
-  <si>
-    <t>Present (nocturia, probable urgency)</t>
-  </si>
-  <si>
-    <t>Present (occasional)</t>
-  </si>
-  <si>
-    <t>Not applicable (Female)</t>
-  </si>
-  <si>
-    <t>Absent (currently)</t>
-  </si>
-  <si>
-    <t>Present (RBD and occasional apneas)</t>
-  </si>
-  <si>
-    <t>Present (low back pain/spine)</t>
-  </si>
-  <si>
-    <t>Presente (lumbago derecho,  crónico)</t>
-  </si>
-  <si>
-    <t>Absent (according to record)</t>
-  </si>
-  <si>
-    <t>Possible / Present (probable)</t>
-  </si>
-  <si>
-    <t>Present (hyposmia)</t>
-  </si>
-  <si>
-    <t>No (under evaluation for DBS)</t>
-  </si>
-  <si>
-    <t>Present (clearly asymmetric parkinsonism)</t>
-  </si>
-  <si>
-    <t>Asymmetry present (Left &gt; Right)</t>
-  </si>
-  <si>
-    <t>Present (motor asymmetry)</t>
-  </si>
-  <si>
-    <t>Asymmetry present (Right &gt; Left)</t>
-  </si>
-  <si>
-    <t>Present (moderate initial asymmetry)</t>
-  </si>
-  <si>
-    <t>Absent (non-tremor-dominant phenotype)</t>
-  </si>
-  <si>
-    <t>Present (tremor-dominant phenotype)</t>
-  </si>
-  <si>
-    <t>Absent (rigid-akinetic phenotype)</t>
-  </si>
-  <si>
-    <t>5 points -&gt; Phenotype more compatible with brain-first</t>
-  </si>
-  <si>
-    <t>6 points -&gt; Intermediate profile, slightly more compatible with body-first</t>
-  </si>
-  <si>
-    <t>&lt;=6 points -&gt; Phenotype more compatible with brain-first</t>
-  </si>
-  <si>
-    <t>7 points -&gt; Profile more compatible with body-first</t>
-  </si>
-  <si>
-    <t>9 puntos → fenotipo más compatible con body-first</t>
-  </si>
-  <si>
-    <t>9 points -&gt; Profile more compatible with body-first</t>
-  </si>
-  <si>
-    <t>8 points -&gt; Profile more compatible with body-first</t>
-  </si>
-  <si>
-    <t>5 points -&gt; Profile more compatible with brain-first</t>
-  </si>
-  <si>
-    <t>Clinically established Parkinson's disease</t>
-  </si>
-  <si>
-    <t>Meets criteria for clinically established Parkinson's disease (MDS 2015)</t>
-  </si>
-  <si>
-    <t>Does not meet criteria for PD</t>
-  </si>
-  <si>
-    <t>Not applicable</t>
-  </si>
-  <si>
-    <t>Severe dysfunction in cardiac parasympathetic reflex activity</t>
-  </si>
-  <si>
-    <t>Cardioprotective diet</t>
-  </si>
-  <si>
-    <t>Diastolic dysfunction, mild insufficiency, moderate effusion</t>
-  </si>
-  <si>
-    <t>Proposed arrhythmia</t>
+    <t>IRC, HTA, polineuropatía mixta, bronconeumonía</t>
+  </si>
+  <si>
+    <t>HTA, Depresión</t>
+  </si>
+  <si>
+    <t>Artrosis</t>
+  </si>
+  <si>
+    <t>Raquiestenosis L4-L5, aneurisma aórtico abdominal operado, gonartrosis rodilla derecha con meniscopatía, posible enfermedad cardiovascular / aterosclerótica leve, enfermedad renal crónica leve</t>
+  </si>
+  <si>
+    <t>Probable trastorno ansioso-depresivo en tratamiento con ISRS; roncopatía con apneas ocasionales del sueño (estimado)</t>
+  </si>
+  <si>
+    <t>Osteoporosis, cáncer cérvico-uterino (en espera de histerectomía), hernia abdominal operada</t>
+  </si>
+  <si>
+    <t>Hipertensión arterial, hipertrigliceridemia, diabetes mellitus tipo 2</t>
+  </si>
+  <si>
+    <t>Hipotiroidismo autoinmune; dislipidemia; prediabetes; quiste aracnoideo de fosa media izquierda; bradicardia sinusal en estudio; disfunción eréctil.</t>
+  </si>
+  <si>
+    <t>Dislipidemia, crisis de pánico, trastorno depresivo, tabaquismo activo, dolor crónico hombro derecho, probable hipovitaminosis D</t>
+  </si>
+  <si>
+    <t>Hipertensión arterial; artrosis de columna con hernia de núcleo pulposo (HNP) lumbar; antecedentes quirúrgicos de hernia umbilical y rotura de tendón de hombro derecho; síntomas ansioso-depresivos en manejo con escitalopram.</t>
+  </si>
+  <si>
+    <t>Dislipidemia; probable trastorno depresivo reactivo; constipación crónica; hiposmia; sialorrea; insomnio de conciliación y sueño fragmentado.</t>
+  </si>
+  <si>
+    <t>Hígado graso, síndrome metabólico, síndrome de túnel carpiano, trastorno depresivo/ansioso</t>
+  </si>
+  <si>
+    <t>HTA, dislipidemia, HPB, Diabetes Mellitus tipo 2, lumbalgia crónica por estenosis foraminal L3-S1 y espondiloartrosis, apnea del sueño en tratamiento con CPAP, disminución agudeza visual.</t>
+  </si>
+  <si>
+    <t>No refiere</t>
+  </si>
+  <si>
+    <t>Ausente</t>
+  </si>
+  <si>
+    <t>Sí (DM2)</t>
+  </si>
+  <si>
+    <t>Ausente (prediabetes)</t>
+  </si>
+  <si>
+    <t>Presente</t>
+  </si>
+  <si>
+    <t>Presentes (antecedente)</t>
+  </si>
+  <si>
+    <t>Ausentes</t>
+  </si>
+  <si>
+    <t>Presente (reactiva, leve-moderada, estimado)</t>
+  </si>
+  <si>
+    <t>Ausente (actualmente, en tratamiento con ISRS) (estimado)</t>
+  </si>
+  <si>
+    <t>Ausente (estimado)</t>
+  </si>
+  <si>
+    <t>Presente (antecedente de tno depresivo, ánimo apático/fluctuante)</t>
+  </si>
+  <si>
+    <t>Presente (síntomas ansioso-depresivos)</t>
+  </si>
+  <si>
+    <t>Presente (reactiva / síntomas depresivos)</t>
+  </si>
+  <si>
+    <t>Presente (leve, estimado)</t>
+  </si>
+  <si>
+    <t>Presentes (urgencia, urge-incontinencia, nicturia)</t>
+  </si>
+  <si>
+    <t>Presentes (nicturia previa, actualmente resuelta)</t>
+  </si>
+  <si>
+    <t>Presentes (nicturia, probable urgencia)</t>
+  </si>
+  <si>
+    <t>No registrados</t>
+  </si>
+  <si>
+    <t>No aplica (sexo femenino)</t>
+  </si>
+  <si>
+    <t>No refiere (estimado)</t>
+  </si>
+  <si>
+    <t>Presentes</t>
+  </si>
+  <si>
+    <t>Presentes (ocasional)</t>
+  </si>
+  <si>
+    <t>Ausente (actualmente)</t>
+  </si>
+  <si>
+    <t>No registrado</t>
+  </si>
+  <si>
+    <t>Presente (leve)</t>
+  </si>
+  <si>
+    <t>Presentes (RBD y apneas ocasionales)</t>
+  </si>
+  <si>
+    <t>Ausentes (actualmente)</t>
+  </si>
+  <si>
+    <t>Presente (lumbalgia/columna, estimado)</t>
+  </si>
+  <si>
+    <t>Presente (lumbago derecho, estimado crónico)</t>
+  </si>
+  <si>
+    <t>No registrada</t>
+  </si>
+  <si>
+    <t>Ausente (según registro)</t>
+  </si>
+  <si>
+    <t>Posibles / Presentes (probables)</t>
+  </si>
+  <si>
+    <t>Presentes (hiposmia)</t>
+  </si>
+  <si>
+    <t>No (en evaluación para DBS)</t>
+  </si>
+  <si>
+    <t>≈1.325 mg/día (estimado, sin contar mucuna)</t>
+  </si>
+  <si>
+    <t>300 mg LED/día</t>
+  </si>
+  <si>
+    <t>≈1.063 mg/día (estimado)</t>
+  </si>
+  <si>
+    <t>300 mg LED/día (estimado)</t>
+  </si>
+  <si>
+    <t>≈150 mg/día (estimado)</t>
+  </si>
+  <si>
+    <t>800 mg LED/día</t>
+  </si>
+  <si>
+    <t>1.250 mg LED/día (estimado)</t>
+  </si>
+  <si>
+    <t>1.000 mg/día</t>
+  </si>
+  <si>
+    <t>150 mg LED/día</t>
+  </si>
+  <si>
+    <t>38 mg LED/día (estimado)</t>
+  </si>
+  <si>
+    <t>≈75 mg LED/día (estimado)</t>
+  </si>
+  <si>
+    <t>0 mg LED/día</t>
+  </si>
+  <si>
+    <t>150 mg/día</t>
+  </si>
+  <si>
+    <t>400 mg LED/día</t>
+  </si>
+  <si>
+    <t>225 mg/día</t>
+  </si>
+  <si>
+    <t>25 mg LED/día</t>
+  </si>
+  <si>
+    <t>≈1.475 mg LED/día (estimado, sin contar mucuna)</t>
+  </si>
+  <si>
+    <t>338 mg LED/día (estimado)</t>
+  </si>
+  <si>
+    <t>≈1.138 mg LED/día (estimado)</t>
+  </si>
+  <si>
+    <t>≈300 mg/día (estimado)</t>
+  </si>
+  <si>
+    <t>900 mg LED/día</t>
+  </si>
+  <si>
+    <t>1.650 mg LED/día (estimado, con nuevo esquema)</t>
+  </si>
+  <si>
+    <t>1.225 mg/día</t>
+  </si>
+  <si>
+    <t>925 mg LED/día (estimado)</t>
+  </si>
+  <si>
+    <t>Presente (parkinsonismo claramente asimétrico)</t>
+  </si>
+  <si>
+    <t>Asimetría presente (izquierda &gt; derecha)</t>
+  </si>
+  <si>
+    <t>Presentes (asimetría motora)</t>
+  </si>
+  <si>
+    <t>Asimetría presente (derecha &gt; izquierda)</t>
+  </si>
+  <si>
+    <t>Asimetría presente (derecha &gt; izquierda) (estimado)</t>
+  </si>
+  <si>
+    <t>Presentes (asimetría inicial moderada)</t>
+  </si>
+  <si>
+    <t>Ausente (fenotipo no temblor-dominante)</t>
+  </si>
+  <si>
+    <t>Presente (estimado)</t>
+  </si>
+  <si>
+    <t>Presente (fenotipo temblor-dominante) (estimado)</t>
+  </si>
+  <si>
+    <t>Presente (fenotipo temblor-dominante)</t>
+  </si>
+  <si>
+    <t>Ausente (fenotipo rígido-akinetico)</t>
+  </si>
+  <si>
+    <t>≈5 puntos → fenotipo más compatible con brain-first (estimado)</t>
+  </si>
+  <si>
+    <t>6 puntos (estimado) → perfil intermedio, ligeramente más compatible con body-first</t>
+  </si>
+  <si>
+    <t>≤6 puntos → fenotipo más compatible con brain-first (estimado)</t>
+  </si>
+  <si>
+    <t>7 puntos (estimado) → perfil más compatible con body-first</t>
+  </si>
+  <si>
+    <t>≈9 puntos → fenotipo más compatible con body-first (estimado)</t>
+  </si>
+  <si>
+    <t>9 puntos (estimado) → Perfil más compatible con body-first</t>
+  </si>
+  <si>
+    <t>8 puntos (estimado) → perfil más compatible con body-first</t>
+  </si>
+  <si>
+    <t>5 puntos → fenotipo más compatible con brain-first</t>
+  </si>
+  <si>
+    <t>5 puntos → Perfil más compatible con brain-first</t>
+  </si>
+  <si>
+    <t>Enfermedad de Parkinson Clínicamente Establecida</t>
+  </si>
+  <si>
+    <t>Cumple criterios de Enfermedad de Parkinson clínicamente establecida (MDS 2015)</t>
+  </si>
+  <si>
+    <t>Enfermedad de Parkinson Clínicamente Establecida (estimado)</t>
+  </si>
+  <si>
+    <t>No cumple criterios para EP</t>
+  </si>
+  <si>
+    <t>No aplica</t>
+  </si>
+  <si>
+    <t>Disfunción diastólica, insuficiencia leve, derrame moderado</t>
+  </si>
+  <si>
+    <t>Dieta Cardioprotectora</t>
+  </si>
+  <si>
+    <t>Pasado operación nodo SA</t>
+  </si>
+  <si>
+    <t>Bradicardia hemicuerpo derecho</t>
+  </si>
+  <si>
+    <t>Planteado Arritmia</t>
   </si>
 </sst>
 </file>
@@ -944,7 +1256,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BM32"/>
+  <dimension ref="A1:BM33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:65">
@@ -1148,62 +1460,62 @@
       <c r="A2" t="s">
         <v>65</v>
       </c>
-      <c r="B2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C2">
+      <c r="B2">
         <v>70</v>
       </c>
-      <c r="D2" t="b">
-        <v>0</v>
+      <c r="C2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>105</v>
       </c>
       <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>60</v>
       </c>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
       </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
       <c r="L2" t="b">
         <v>0</v>
       </c>
-      <c r="M2">
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2">
         <v>3</v>
       </c>
-      <c r="N2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2">
+      <c r="P2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q2">
         <v>60</v>
       </c>
-      <c r="P2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q2">
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <v>4</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2">
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2">
         <v>5</v>
-      </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>3</v>
       </c>
       <c r="V2" t="b">
         <v>0</v>
@@ -1215,25 +1527,25 @@
         <v>0</v>
       </c>
       <c r="Y2">
+        <v>3</v>
+      </c>
+      <c r="Z2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA2">
         <v>15</v>
       </c>
-      <c r="Z2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>115</v>
-      </c>
       <c r="AB2" t="b">
         <v>0</v>
       </c>
-      <c r="AD2">
-        <v>1</v>
-      </c>
-      <c r="AE2">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="b">
-        <v>0</v>
+      <c r="AC2" t="s">
+        <v>180</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
       </c>
       <c r="AG2">
         <v>1</v>
@@ -1244,37 +1556,40 @@
       <c r="AI2">
         <v>1</v>
       </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>1</v>
+      <c r="AJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>225</v>
+      </c>
+      <c r="AM2" t="b">
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>1</v>
       </c>
       <c r="AP2">
         <v>1</v>
       </c>
-      <c r="AQ2">
-        <v>1</v>
+      <c r="AQ2" t="b">
+        <v>0</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
         <v>0</v>
       </c>
       <c r="AW2" t="b">
@@ -1289,50 +1604,47 @@
       <c r="BC2" t="b">
         <v>0</v>
       </c>
-      <c r="BF2" t="b">
+      <c r="BE2" t="b">
         <v>0</v>
       </c>
       <c r="BH2" t="b">
         <v>0</v>
       </c>
-      <c r="BI2">
+      <c r="BJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK2">
         <v>3</v>
       </c>
-      <c r="BJ2">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>186</v>
-      </c>
       <c r="BL2">
-        <v>10</v>
-      </c>
-      <c r="BM2" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:65">
       <c r="A3" t="s">
         <v>66</v>
       </c>
-      <c r="B3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3">
-        <v>54</v>
-      </c>
-      <c r="D3" t="b">
-        <v>0</v>
+      <c r="B3">
+        <v>58</v>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>105</v>
       </c>
       <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>53</v>
       </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
@@ -1342,65 +1654,68 @@
       <c r="J3" t="b">
         <v>0</v>
       </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
       <c r="L3" t="b">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
       <c r="N3" t="b">
         <v>0</v>
       </c>
       <c r="O3">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
       </c>
       <c r="Q3">
+        <v>80</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>3</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>3</v>
+      </c>
+      <c r="V3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3">
         <v>2</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>1</v>
-      </c>
-      <c r="V3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>1</v>
-      </c>
       <c r="X3" t="b">
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
       </c>
+      <c r="AA3">
+        <v>10</v>
+      </c>
       <c r="AB3" t="b">
         <v>0</v>
       </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="b">
+      <c r="AC3" t="s">
+        <v>181</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3">
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="b">
         <v>0</v>
@@ -1408,37 +1723,40 @@
       <c r="AI3">
         <v>0</v>
       </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>1</v>
-      </c>
-      <c r="AM3">
+      <c r="AJ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>225</v>
+      </c>
+      <c r="AM3" t="b">
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>1</v>
       </c>
       <c r="AP3">
         <v>1</v>
       </c>
-      <c r="AQ3">
+      <c r="AQ3" t="b">
         <v>0</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT3">
+        <v>1</v>
+      </c>
+      <c r="AU3">
         <v>0</v>
       </c>
       <c r="AW3" t="b">
@@ -1453,82 +1771,79 @@
       <c r="BC3" t="b">
         <v>0</v>
       </c>
-      <c r="BF3" t="b">
+      <c r="BE3" t="b">
         <v>0</v>
       </c>
       <c r="BH3" t="b">
         <v>0</v>
       </c>
-      <c r="BI3">
-        <v>1</v>
-      </c>
-      <c r="BJ3">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>186</v>
+      <c r="BJ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>1</v>
       </c>
       <c r="BL3">
-        <v>1</v>
-      </c>
-      <c r="BM3" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:65">
       <c r="A4" t="s">
         <v>67</v>
       </c>
-      <c r="B4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4">
-        <v>69</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
+      <c r="B4">
+        <v>65</v>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>106</v>
       </c>
       <c r="E4">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
       </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
       <c r="L4" t="b">
         <v>0</v>
       </c>
-      <c r="M4">
-        <v>3</v>
-      </c>
       <c r="N4" t="b">
         <v>0</v>
       </c>
       <c r="O4">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -1540,168 +1855,168 @@
         <v>0</v>
       </c>
       <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>6</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>182</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>1</v>
+      </c>
+      <c r="AP4">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>1</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK4">
         <v>2</v>
       </c>
-      <c r="X4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>11</v>
-      </c>
-      <c r="Z4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>116</v>
-      </c>
-      <c r="AB4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>1</v>
-      </c>
-      <c r="AE4">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>1</v>
-      </c>
-      <c r="AH4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>1</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>1</v>
-      </c>
-      <c r="AN4">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>1</v>
-      </c>
-      <c r="AQ4">
-        <v>1</v>
-      </c>
-      <c r="AR4">
-        <v>1</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BI4">
-        <v>3</v>
-      </c>
-      <c r="BJ4">
-        <v>0</v>
-      </c>
-      <c r="BK4" t="s">
-        <v>186</v>
-      </c>
       <c r="BL4">
-        <v>6</v>
-      </c>
-      <c r="BM4" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:65">
       <c r="A5" t="s">
         <v>68</v>
       </c>
-      <c r="B5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5">
-        <v>64</v>
-      </c>
-      <c r="D5" t="b">
-        <v>0</v>
+      <c r="B5">
+        <v>65</v>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>106</v>
       </c>
       <c r="E5">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
       <c r="N5" t="b">
         <v>0</v>
       </c>
       <c r="O5">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" t="b">
         <v>0</v>
@@ -1713,57 +2028,57 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
       </c>
-      <c r="AA5" t="s">
-        <v>117</v>
+      <c r="AA5">
+        <v>8</v>
       </c>
       <c r="AB5" t="b">
         <v>0</v>
       </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="b">
+      <c r="AC5" t="s">
+        <v>183</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5">
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5" t="b">
         <v>0</v>
       </c>
       <c r="AI5">
-        <v>1</v>
-      </c>
-      <c r="AJ5">
-        <v>1</v>
-      </c>
-      <c r="AK5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK5">
         <v>0</v>
       </c>
       <c r="AL5">
         <v>1</v>
       </c>
-      <c r="AM5">
+      <c r="AM5" t="b">
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>1</v>
       </c>
       <c r="AP5">
         <v>1</v>
       </c>
-      <c r="AQ5">
+      <c r="AQ5" t="b">
         <v>0</v>
       </c>
       <c r="AR5">
@@ -1772,7 +2087,10 @@
       <c r="AS5">
         <v>0</v>
       </c>
-      <c r="AU5" t="b">
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
         <v>0</v>
       </c>
       <c r="AW5" t="b">
@@ -1787,117 +2105,114 @@
       <c r="BC5" t="b">
         <v>0</v>
       </c>
-      <c r="BF5" t="b">
+      <c r="BE5" t="b">
         <v>0</v>
       </c>
       <c r="BH5" t="b">
         <v>0</v>
       </c>
-      <c r="BI5">
-        <v>3</v>
-      </c>
-      <c r="BJ5">
-        <v>0</v>
-      </c>
-      <c r="BK5" t="s">
-        <v>186</v>
+      <c r="BJ5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>2</v>
       </c>
       <c r="BL5">
         <v>1</v>
       </c>
-      <c r="BM5" t="b">
-        <v>0</v>
+      <c r="BM5" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:65">
       <c r="A6" t="s">
         <v>69</v>
       </c>
-      <c r="B6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6">
+      <c r="B6">
+        <v>68</v>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6">
+        <v>15</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>53</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>3</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6">
         <v>65</v>
       </c>
-      <c r="D6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>53</v>
-      </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>1.5</v>
-      </c>
-      <c r="N6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0.9</v>
-      </c>
-      <c r="P6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>2</v>
-      </c>
       <c r="R6" t="b">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V6" t="b">
         <v>0</v>
       </c>
       <c r="W6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
       </c>
-      <c r="AA6" t="s">
-        <v>118</v>
+      <c r="AA6">
+        <v>13</v>
       </c>
       <c r="AB6" t="b">
         <v>0</v>
       </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="b">
+      <c r="AC6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6">
         <v>0</v>
       </c>
       <c r="AG6">
@@ -1907,39 +2222,42 @@
         <v>0</v>
       </c>
       <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>1</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
-      <c r="AM6">
-        <v>1</v>
+      <c r="AM6" t="b">
+        <v>0</v>
       </c>
       <c r="AN6">
         <v>1</v>
       </c>
-      <c r="AO6" t="b">
-        <v>0</v>
+      <c r="AO6">
+        <v>1</v>
       </c>
       <c r="AP6">
         <v>1</v>
       </c>
-      <c r="AQ6">
+      <c r="AQ6" t="b">
         <v>0</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT6">
+        <v>1</v>
+      </c>
+      <c r="AU6">
         <v>0</v>
       </c>
       <c r="AW6" t="b">
@@ -1954,76 +2272,73 @@
       <c r="BC6" t="b">
         <v>0</v>
       </c>
-      <c r="BF6" t="b">
+      <c r="BE6" t="b">
         <v>0</v>
       </c>
       <c r="BH6" t="b">
         <v>0</v>
       </c>
-      <c r="BI6">
-        <v>2</v>
-      </c>
-      <c r="BJ6">
-        <v>0</v>
-      </c>
-      <c r="BK6" t="s">
-        <v>186</v>
+      <c r="BJ6" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>4</v>
       </c>
       <c r="BL6">
-        <v>12</v>
-      </c>
-      <c r="BM6" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:65">
       <c r="A7" t="s">
         <v>70</v>
       </c>
-      <c r="B7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7">
+      <c r="B7">
         <v>70</v>
       </c>
-      <c r="D7" t="b">
-        <v>0</v>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>106</v>
       </c>
       <c r="E7">
+        <v>13</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>57</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
       <c r="L7" t="b">
         <v>0</v>
       </c>
-      <c r="M7">
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7">
         <v>3</v>
       </c>
-      <c r="N7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O7">
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7">
         <v>70</v>
-      </c>
-      <c r="P7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>4</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
@@ -2035,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V7" t="b">
         <v>0</v>
@@ -2047,69 +2362,69 @@
         <v>0</v>
       </c>
       <c r="Y7">
+        <v>3</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7">
         <v>14</v>
       </c>
-      <c r="Z7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>119</v>
-      </c>
       <c r="AB7" t="b">
         <v>0</v>
       </c>
-      <c r="AC7">
-        <v>1</v>
-      </c>
-      <c r="AD7">
-        <v>1</v>
-      </c>
-      <c r="AE7">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="b">
-        <v>0</v>
+      <c r="AC7" t="s">
+        <v>185</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>1</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH7" t="b">
         <v>0</v>
       </c>
       <c r="AI7">
-        <v>1</v>
-      </c>
-      <c r="AJ7">
-        <v>1</v>
-      </c>
-      <c r="AK7" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>1</v>
       </c>
       <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AM7" t="b">
+        <v>0</v>
       </c>
       <c r="AN7">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>1</v>
       </c>
       <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="b">
         <v>0</v>
       </c>
       <c r="AR7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS7">
         <v>0</v>
       </c>
-      <c r="AU7" t="b">
+      <c r="AT7">
+        <v>1</v>
+      </c>
+      <c r="AU7">
         <v>0</v>
       </c>
       <c r="AW7" t="b">
@@ -2124,437 +2439,449 @@
       <c r="BC7" t="b">
         <v>0</v>
       </c>
-      <c r="BF7" t="b">
+      <c r="BE7" t="b">
         <v>0</v>
       </c>
       <c r="BH7" t="b">
         <v>0</v>
       </c>
+      <c r="BJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>3</v>
+      </c>
       <c r="BL7">
-        <v>13</v>
-      </c>
-      <c r="BM7" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="8" spans="1:65">
       <c r="A8" t="s">
         <v>71</v>
       </c>
-      <c r="B8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8">
-        <v>72</v>
-      </c>
-      <c r="D8" t="b">
-        <v>0</v>
+      <c r="B8">
+        <v>55</v>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>106</v>
       </c>
       <c r="E8">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
-      <c r="M8">
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>2</v>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>80</v>
+      </c>
+      <c r="R8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>3</v>
       </c>
-      <c r="N8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>65</v>
-      </c>
-      <c r="P8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q8">
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>2</v>
+      </c>
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>2</v>
+      </c>
+      <c r="Z8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>8</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>186</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>1</v>
+      </c>
+      <c r="AO8">
+        <v>1</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>1</v>
+      </c>
+      <c r="AS8">
+        <v>1</v>
+      </c>
+      <c r="AT8">
+        <v>1</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK8">
         <v>3</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>4</v>
-      </c>
-      <c r="T8" t="b">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>3</v>
-      </c>
-      <c r="V8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>2</v>
-      </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>12</v>
-      </c>
-      <c r="Z8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>120</v>
-      </c>
-      <c r="AB8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>1</v>
-      </c>
-      <c r="AH8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI8">
-        <v>1</v>
-      </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>1</v>
-      </c>
-      <c r="AN8">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>1</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="b">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="b">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="b">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="b">
-        <v>0</v>
-      </c>
-      <c r="BI8">
-        <v>3</v>
-      </c>
-      <c r="BJ8">
-        <v>0</v>
-      </c>
-      <c r="BK8" t="s">
-        <v>186</v>
-      </c>
       <c r="BL8">
-        <v>8</v>
-      </c>
-      <c r="BM8" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="9" spans="1:65">
       <c r="A9" t="s">
         <v>72</v>
       </c>
-      <c r="B9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9">
-        <v>57</v>
-      </c>
-      <c r="D9" t="b">
-        <v>0</v>
+      <c r="B9">
+        <v>64</v>
+      </c>
+      <c r="C9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>106</v>
       </c>
       <c r="E9">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
       <c r="L9" t="b">
         <v>0</v>
       </c>
-      <c r="M9">
-        <v>2</v>
-      </c>
       <c r="N9" t="b">
         <v>0</v>
       </c>
       <c r="O9">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
       </c>
       <c r="Q9">
+        <v>95</v>
+      </c>
+      <c r="R9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9">
         <v>3</v>
       </c>
-      <c r="R9" t="b">
-        <v>0</v>
-      </c>
-      <c r="S9">
+      <c r="AB9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>187</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>1</v>
+      </c>
+      <c r="AL9">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>1</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>1</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>1</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK9">
         <v>3</v>
       </c>
-      <c r="T9" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>2</v>
-      </c>
-      <c r="V9" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>2</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>10</v>
-      </c>
-      <c r="Z9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI9">
-        <v>0</v>
-      </c>
-      <c r="AJ9">
-        <v>1</v>
-      </c>
-      <c r="AK9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL9">
-        <v>1</v>
-      </c>
-      <c r="AM9">
-        <v>1</v>
-      </c>
-      <c r="AN9">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>1</v>
-      </c>
-      <c r="AS9">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="b">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="b">
-        <v>0</v>
-      </c>
-      <c r="BF9" t="b">
-        <v>0</v>
-      </c>
-      <c r="BH9" t="b">
-        <v>0</v>
-      </c>
-      <c r="BI9">
-        <v>3</v>
-      </c>
-      <c r="BJ9">
-        <v>0</v>
-      </c>
-      <c r="BK9" t="s">
-        <v>186</v>
-      </c>
       <c r="BL9">
-        <v>5</v>
-      </c>
-      <c r="BM9" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="10" spans="1:65">
       <c r="A10" t="s">
         <v>73</v>
       </c>
-      <c r="B10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10">
-        <v>55</v>
-      </c>
-      <c r="D10" t="b">
-        <v>0</v>
+      <c r="B10">
+        <v>56</v>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>106</v>
       </c>
       <c r="E10">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
-      <c r="M10">
-        <v>2</v>
-      </c>
       <c r="N10" t="b">
         <v>0</v>
       </c>
       <c r="O10">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="P10" t="b">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
       <c r="S10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
       </c>
       <c r="U10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V10" t="b">
         <v>0</v>
       </c>
       <c r="W10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X10" t="b">
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
       </c>
+      <c r="AA10">
+        <v>18</v>
+      </c>
       <c r="AB10" t="b">
         <v>0</v>
       </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="b">
-        <v>0</v>
+      <c r="AC10" t="s">
+        <v>185</v>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>1</v>
       </c>
       <c r="AG10">
         <v>1</v>
@@ -2563,39 +2890,42 @@
         <v>0</v>
       </c>
       <c r="AI10">
-        <v>0</v>
-      </c>
-      <c r="AJ10">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>1</v>
       </c>
       <c r="AL10">
         <v>1</v>
       </c>
-      <c r="AM10">
+      <c r="AM10" t="b">
         <v>0</v>
       </c>
       <c r="AN10">
         <v>1</v>
       </c>
-      <c r="AO10" t="b">
-        <v>0</v>
+      <c r="AO10">
+        <v>1</v>
       </c>
       <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
+        <v>1</v>
+      </c>
+      <c r="AQ10" t="b">
         <v>0</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS10">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT10">
+        <v>1</v>
+      </c>
+      <c r="AU10">
         <v>0</v>
       </c>
       <c r="AW10" t="b">
@@ -2610,73 +2940,79 @@
       <c r="BC10" t="b">
         <v>0</v>
       </c>
-      <c r="BF10" t="b">
+      <c r="BE10" t="b">
         <v>0</v>
       </c>
       <c r="BH10" t="b">
         <v>0</v>
       </c>
+      <c r="BJ10" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>5</v>
+      </c>
       <c r="BL10">
-        <v>3</v>
-      </c>
-      <c r="BM10" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BM10" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:65">
       <c r="A11" t="s">
         <v>74</v>
       </c>
-      <c r="B11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11">
-        <v>75</v>
-      </c>
-      <c r="D11" t="b">
-        <v>0</v>
+      <c r="B11">
+        <v>55</v>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>106</v>
       </c>
       <c r="E11">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
       </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
       <c r="L11" t="b">
         <v>0</v>
       </c>
-      <c r="M11">
+      <c r="N11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>2</v>
+      </c>
+      <c r="P11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>80</v>
+      </c>
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11">
         <v>3</v>
-      </c>
-      <c r="N11" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>70</v>
-      </c>
-      <c r="P11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>4</v>
-      </c>
-      <c r="R11" t="b">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>4</v>
       </c>
       <c r="T11" t="b">
         <v>0</v>
@@ -2694,24 +3030,24 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
       </c>
-      <c r="AA11" t="s">
-        <v>121</v>
+      <c r="AA11">
+        <v>10</v>
       </c>
       <c r="AB11" t="b">
         <v>0</v>
       </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="b">
+      <c r="AC11" t="s">
+        <v>188</v>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11">
         <v>0</v>
       </c>
       <c r="AG11">
@@ -2721,31 +3057,31 @@
         <v>0</v>
       </c>
       <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK11">
         <v>0</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
-      <c r="AM11">
+      <c r="AM11" t="b">
         <v>0</v>
       </c>
       <c r="AN11">
         <v>1</v>
       </c>
-      <c r="AO11" t="b">
+      <c r="AO11">
         <v>0</v>
       </c>
       <c r="AP11">
         <v>1</v>
       </c>
-      <c r="AQ11">
-        <v>1</v>
+      <c r="AQ11" t="b">
+        <v>0</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -2753,7 +3089,10 @@
       <c r="AS11">
         <v>0</v>
       </c>
-      <c r="AU11" t="b">
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
         <v>0</v>
       </c>
       <c r="AW11" t="b">
@@ -2768,49 +3107,46 @@
       <c r="BC11" t="b">
         <v>0</v>
       </c>
-      <c r="BF11" t="b">
+      <c r="BE11" t="b">
         <v>0</v>
       </c>
       <c r="BH11" t="b">
         <v>0</v>
       </c>
-      <c r="BI11">
-        <v>0</v>
-      </c>
-      <c r="BJ11">
-        <v>1</v>
-      </c>
-      <c r="BK11" t="s">
-        <v>187</v>
+      <c r="BJ11" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>2</v>
       </c>
       <c r="BL11">
-        <v>8</v>
-      </c>
-      <c r="BM11" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BM11" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:65">
       <c r="A12" t="s">
         <v>75</v>
       </c>
-      <c r="B12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12">
-        <v>55</v>
-      </c>
-      <c r="D12" t="b">
-        <v>0</v>
+      <c r="B12">
+        <v>69</v>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>106</v>
       </c>
       <c r="E12">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -2821,29 +3157,29 @@
       <c r="J12" t="b">
         <v>0</v>
       </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
       <c r="L12" t="b">
         <v>0</v>
       </c>
-      <c r="M12">
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12">
         <v>2</v>
       </c>
-      <c r="N12" t="b">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>80</v>
-      </c>
       <c r="P12" t="b">
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T12" t="b">
         <v>0</v>
@@ -2861,25 +3197,28 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="b">
         <v>0</v>
       </c>
+      <c r="AA12">
+        <v>7</v>
+      </c>
       <c r="AB12" t="b">
         <v>0</v>
       </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="b">
-        <v>0</v>
+      <c r="AC12" t="s">
+        <v>189</v>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>1</v>
       </c>
       <c r="AG12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="b">
         <v>0</v>
@@ -2887,28 +3226,28 @@
       <c r="AI12">
         <v>0</v>
       </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="b">
-        <v>0</v>
+      <c r="AJ12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>1</v>
       </c>
       <c r="AL12">
         <v>1</v>
       </c>
-      <c r="AM12">
+      <c r="AM12" t="b">
         <v>0</v>
       </c>
       <c r="AN12">
-        <v>1</v>
-      </c>
-      <c r="AO12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
         <v>0</v>
       </c>
-      <c r="AQ12">
+      <c r="AQ12" t="b">
         <v>0</v>
       </c>
       <c r="AR12">
@@ -2917,7 +3256,10 @@
       <c r="AS12">
         <v>0</v>
       </c>
-      <c r="AU12" t="b">
+      <c r="AT12">
+        <v>1</v>
+      </c>
+      <c r="AU12">
         <v>0</v>
       </c>
       <c r="AW12" t="b">
@@ -2932,76 +3274,73 @@
       <c r="BC12" t="b">
         <v>0</v>
       </c>
-      <c r="BF12" t="b">
+      <c r="BE12" t="b">
         <v>0</v>
       </c>
       <c r="BH12" t="b">
         <v>0</v>
       </c>
-      <c r="BI12">
-        <v>2</v>
-      </c>
-      <c r="BJ12">
-        <v>1</v>
-      </c>
-      <c r="BK12" t="s">
-        <v>188</v>
+      <c r="BJ12" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
       </c>
       <c r="BL12">
-        <v>3</v>
-      </c>
-      <c r="BM12" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BM12" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="13" spans="1:65">
       <c r="A13" t="s">
         <v>76</v>
       </c>
-      <c r="B13" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13">
+      <c r="B13">
         <v>71</v>
       </c>
-      <c r="D13" t="b">
-        <v>0</v>
+      <c r="C13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
+        <v>106</v>
       </c>
       <c r="E13">
+        <v>16</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>55</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
-      <c r="M13">
+      <c r="N13" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13">
         <v>2</v>
       </c>
-      <c r="N13" t="b">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0.8</v>
-      </c>
       <c r="P13" t="b">
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
@@ -3013,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V13" t="b">
         <v>0</v>
@@ -3025,25 +3364,25 @@
         <v>0</v>
       </c>
       <c r="Y13">
+        <v>2</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA13">
         <v>12</v>
       </c>
-      <c r="Z13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>122</v>
-      </c>
       <c r="AB13" t="b">
         <v>0</v>
       </c>
-      <c r="AD13">
-        <v>1</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="b">
-        <v>0</v>
+      <c r="AC13" t="s">
+        <v>190</v>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>1</v>
       </c>
       <c r="AG13">
         <v>0</v>
@@ -3052,39 +3391,42 @@
         <v>0</v>
       </c>
       <c r="AI13">
-        <v>1</v>
-      </c>
-      <c r="AJ13">
-        <v>1</v>
-      </c>
-      <c r="AK13" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>1</v>
       </c>
       <c r="AL13">
         <v>1</v>
       </c>
-      <c r="AM13">
-        <v>1</v>
+      <c r="AM13" t="b">
+        <v>0</v>
       </c>
       <c r="AN13">
         <v>1</v>
       </c>
-      <c r="AO13" t="b">
-        <v>0</v>
+      <c r="AO13">
+        <v>1</v>
       </c>
       <c r="AP13">
         <v>1</v>
       </c>
-      <c r="AQ13">
-        <v>1</v>
+      <c r="AQ13" t="b">
+        <v>0</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
         <v>0</v>
       </c>
       <c r="AW13" t="b">
@@ -3099,121 +3441,118 @@
       <c r="BC13" t="b">
         <v>0</v>
       </c>
-      <c r="BF13" t="b">
+      <c r="BE13" t="b">
         <v>0</v>
       </c>
       <c r="BH13" t="b">
         <v>0</v>
       </c>
-      <c r="BI13">
+      <c r="BJ13" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK13">
         <v>4</v>
       </c>
-      <c r="BJ13">
-        <v>0</v>
-      </c>
-      <c r="BK13" t="s">
-        <v>186</v>
-      </c>
       <c r="BL13">
-        <v>16</v>
-      </c>
-      <c r="BM13" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BM13" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="14" spans="1:65">
       <c r="A14" t="s">
         <v>77</v>
       </c>
-      <c r="B14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C14">
-        <v>69</v>
-      </c>
-      <c r="D14" t="b">
-        <v>0</v>
+      <c r="B14">
+        <v>72</v>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>105</v>
       </c>
       <c r="E14">
+        <v>8</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>64</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>3</v>
+      </c>
+      <c r="P14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14">
         <v>65</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14">
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>3</v>
+      </c>
+      <c r="T14" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>4</v>
+      </c>
+      <c r="V14" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>3</v>
+      </c>
+      <c r="X14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y14">
         <v>2</v>
       </c>
-      <c r="N14" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0.9</v>
-      </c>
-      <c r="P14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>2</v>
-      </c>
-      <c r="R14" t="b">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>2</v>
-      </c>
-      <c r="T14" t="b">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>2</v>
-      </c>
-      <c r="V14" t="b">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>1</v>
-      </c>
-      <c r="X14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>7</v>
-      </c>
       <c r="Z14" t="b">
         <v>0</v>
       </c>
-      <c r="AA14" t="s">
-        <v>123</v>
+      <c r="AA14">
+        <v>12</v>
       </c>
       <c r="AB14" t="b">
         <v>0</v>
       </c>
-      <c r="AD14">
-        <v>1</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="b">
+      <c r="AC14" t="s">
+        <v>183</v>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14">
         <v>0</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="b">
         <v>0</v>
@@ -3221,37 +3560,40 @@
       <c r="AI14">
         <v>1</v>
       </c>
-      <c r="AJ14">
-        <v>1</v>
-      </c>
-      <c r="AK14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
+      <c r="AJ14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>1</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>225</v>
+      </c>
+      <c r="AM14" t="b">
         <v>0</v>
       </c>
       <c r="AN14">
         <v>0</v>
       </c>
-      <c r="AO14" t="b">
-        <v>0</v>
+      <c r="AO14">
+        <v>1</v>
       </c>
       <c r="AP14">
-        <v>0</v>
-      </c>
-      <c r="AQ14">
+        <v>1</v>
+      </c>
+      <c r="AQ14" t="b">
         <v>0</v>
       </c>
       <c r="AR14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS14">
         <v>0</v>
       </c>
-      <c r="AU14" t="b">
+      <c r="AT14">
+        <v>1</v>
+      </c>
+      <c r="AU14">
         <v>0</v>
       </c>
       <c r="AW14" t="b">
@@ -3266,49 +3608,46 @@
       <c r="BC14" t="b">
         <v>0</v>
       </c>
-      <c r="BF14" t="b">
+      <c r="BE14" t="b">
         <v>0</v>
       </c>
       <c r="BH14" t="b">
         <v>0</v>
       </c>
-      <c r="BI14">
-        <v>0</v>
-      </c>
-      <c r="BJ14">
-        <v>0</v>
-      </c>
-      <c r="BK14" t="s">
-        <v>186</v>
+      <c r="BJ14" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>3</v>
       </c>
       <c r="BL14">
-        <v>4</v>
-      </c>
-      <c r="BM14" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BM14" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="15" spans="1:65">
       <c r="A15" t="s">
         <v>78</v>
       </c>
-      <c r="B15" t="s">
-        <v>96</v>
-      </c>
-      <c r="C15">
-        <v>58</v>
-      </c>
-      <c r="D15" t="b">
-        <v>0</v>
+      <c r="B15">
+        <v>85</v>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>105</v>
       </c>
       <c r="E15">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -3319,23 +3658,23 @@
       <c r="J15" t="b">
         <v>0</v>
       </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
       <c r="L15" t="b">
         <v>0</v>
       </c>
-      <c r="M15">
+      <c r="N15" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15">
         <v>2</v>
       </c>
-      <c r="N15" t="b">
-        <v>0</v>
-      </c>
-      <c r="O15">
+      <c r="P15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q15">
         <v>80</v>
-      </c>
-      <c r="P15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>3</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
@@ -3347,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V15" t="b">
         <v>0</v>
@@ -3359,66 +3698,69 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Z15" t="b">
         <v>0</v>
       </c>
-      <c r="AA15" t="s">
-        <v>124</v>
+      <c r="AA15">
+        <v>11</v>
       </c>
       <c r="AB15" t="b">
         <v>0</v>
       </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="b">
+      <c r="AC15" t="s">
+        <v>191</v>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15">
         <v>0</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH15" t="b">
         <v>0</v>
       </c>
       <c r="AI15">
-        <v>0</v>
-      </c>
-      <c r="AJ15">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AJ15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>1</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>225</v>
+      </c>
+      <c r="AM15" t="b">
+        <v>0</v>
       </c>
       <c r="AN15">
         <v>1</v>
       </c>
-      <c r="AO15" t="b">
-        <v>0</v>
+      <c r="AO15">
+        <v>1</v>
       </c>
       <c r="AP15">
-        <v>1</v>
-      </c>
-      <c r="AQ15">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="b">
+        <v>0</v>
       </c>
       <c r="AR15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS15">
         <v>0</v>
       </c>
-      <c r="AU15" t="b">
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
         <v>0</v>
       </c>
       <c r="AW15" t="b">
@@ -3433,82 +3775,79 @@
       <c r="BC15" t="b">
         <v>0</v>
       </c>
-      <c r="BF15" t="b">
+      <c r="BE15" t="b">
         <v>0</v>
       </c>
       <c r="BH15" t="b">
         <v>0</v>
       </c>
-      <c r="BI15">
-        <v>1</v>
-      </c>
-      <c r="BJ15">
-        <v>0</v>
-      </c>
-      <c r="BK15" t="s">
-        <v>186</v>
+      <c r="BJ15" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>4</v>
       </c>
       <c r="BL15">
-        <v>5</v>
-      </c>
-      <c r="BM15" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BM15" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:65">
       <c r="A16" t="s">
         <v>79</v>
       </c>
-      <c r="B16" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16">
-        <v>62</v>
-      </c>
-      <c r="D16" t="b">
-        <v>0</v>
+      <c r="B16">
+        <v>68</v>
+      </c>
+      <c r="C16" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
+        <v>105</v>
       </c>
       <c r="E16">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
       </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
-      <c r="M16">
+      <c r="N16" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>2</v>
+      </c>
+      <c r="P16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>75</v>
+      </c>
+      <c r="R16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16">
         <v>3</v>
-      </c>
-      <c r="N16" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>75</v>
-      </c>
-      <c r="P16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>4</v>
-      </c>
-      <c r="R16" t="b">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>4</v>
       </c>
       <c r="T16" t="b">
         <v>0</v>
@@ -3520,30 +3859,30 @@
         <v>0</v>
       </c>
       <c r="W16">
+        <v>2</v>
+      </c>
+      <c r="X16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y16">
         <v>3</v>
       </c>
-      <c r="X16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>14</v>
-      </c>
       <c r="Z16" t="b">
         <v>0</v>
       </c>
-      <c r="AA16" t="s">
-        <v>125</v>
+      <c r="AA16">
+        <v>11</v>
       </c>
       <c r="AB16" t="b">
         <v>0</v>
       </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="b">
+      <c r="AC16" t="s">
+        <v>192</v>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16">
         <v>0</v>
       </c>
       <c r="AG16">
@@ -3555,29 +3894,29 @@
       <c r="AI16">
         <v>1</v>
       </c>
-      <c r="AJ16">
-        <v>1</v>
-      </c>
-      <c r="AK16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL16">
-        <v>1</v>
-      </c>
-      <c r="AM16">
-        <v>1</v>
+      <c r="AJ16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>225</v>
+      </c>
+      <c r="AM16" t="b">
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>1</v>
-      </c>
-      <c r="AO16" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>1</v>
       </c>
       <c r="AP16">
         <v>1</v>
       </c>
-      <c r="AQ16">
-        <v>1</v>
+      <c r="AQ16" t="b">
+        <v>0</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -3585,7 +3924,10 @@
       <c r="AS16">
         <v>0</v>
       </c>
-      <c r="AU16" t="b">
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
         <v>0</v>
       </c>
       <c r="AW16" t="b">
@@ -3600,121 +3942,118 @@
       <c r="BC16" t="b">
         <v>0</v>
       </c>
-      <c r="BF16" t="b">
+      <c r="BE16" t="b">
         <v>0</v>
       </c>
       <c r="BH16" t="b">
         <v>0</v>
       </c>
-      <c r="BI16">
-        <v>5</v>
-      </c>
-      <c r="BJ16">
-        <v>0</v>
-      </c>
-      <c r="BK16" t="s">
-        <v>186</v>
+      <c r="BJ16" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>2</v>
       </c>
       <c r="BL16">
-        <v>7</v>
-      </c>
-      <c r="BM16" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BM16" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="17" spans="1:65">
       <c r="A17" t="s">
         <v>80</v>
       </c>
-      <c r="B17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C17">
-        <v>59</v>
-      </c>
-      <c r="D17" t="b">
-        <v>0</v>
+      <c r="B17">
+        <v>57</v>
+      </c>
+      <c r="C17" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" t="s">
+        <v>106</v>
       </c>
       <c r="E17">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
       </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
       <c r="L17" t="b">
         <v>0</v>
       </c>
-      <c r="M17">
+      <c r="N17" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17">
         <v>2</v>
       </c>
-      <c r="N17" t="b">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>80</v>
-      </c>
       <c r="P17" t="b">
         <v>0</v>
       </c>
       <c r="Q17">
+        <v>85</v>
+      </c>
+      <c r="R17" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17">
         <v>3</v>
       </c>
-      <c r="R17" t="b">
-        <v>0</v>
-      </c>
-      <c r="S17">
+      <c r="T17" t="b">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>3</v>
+      </c>
+      <c r="V17" t="b">
+        <v>0</v>
+      </c>
+      <c r="W17">
         <v>2</v>
       </c>
-      <c r="T17" t="b">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>1</v>
-      </c>
-      <c r="V17" t="b">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>1</v>
-      </c>
       <c r="X17" t="b">
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z17" t="b">
         <v>0</v>
       </c>
-      <c r="AA17" t="s">
-        <v>126</v>
+      <c r="AA17">
+        <v>10</v>
       </c>
       <c r="AB17" t="b">
         <v>0</v>
       </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="b">
+      <c r="AC17" t="s">
+        <v>188</v>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17">
         <v>0</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH17" t="b">
         <v>0</v>
@@ -3722,28 +4061,28 @@
       <c r="AI17">
         <v>0</v>
       </c>
-      <c r="AJ17">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="b">
+      <c r="AJ17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK17">
         <v>0</v>
       </c>
       <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
+        <v>1</v>
+      </c>
+      <c r="AM17" t="b">
         <v>0</v>
       </c>
       <c r="AN17">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AO17">
+        <v>1</v>
       </c>
       <c r="AP17">
         <v>0</v>
       </c>
-      <c r="AQ17">
+      <c r="AQ17" t="b">
         <v>0</v>
       </c>
       <c r="AR17">
@@ -3752,7 +4091,10 @@
       <c r="AS17">
         <v>0</v>
       </c>
-      <c r="AU17" t="b">
+      <c r="AT17">
+        <v>1</v>
+      </c>
+      <c r="AU17">
         <v>0</v>
       </c>
       <c r="AW17" t="b">
@@ -3767,49 +4109,46 @@
       <c r="BC17" t="b">
         <v>0</v>
       </c>
-      <c r="BF17" t="b">
+      <c r="BE17" t="b">
         <v>0</v>
       </c>
       <c r="BH17" t="b">
         <v>0</v>
       </c>
-      <c r="BI17">
-        <v>0</v>
-      </c>
-      <c r="BJ17">
-        <v>0</v>
-      </c>
-      <c r="BK17" t="s">
-        <v>186</v>
+      <c r="BJ17" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>3</v>
       </c>
       <c r="BL17">
-        <v>3</v>
-      </c>
-      <c r="BM17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BM17" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="18" spans="1:65">
       <c r="A18" t="s">
         <v>81</v>
       </c>
-      <c r="B18" t="s">
-        <v>97</v>
-      </c>
-      <c r="C18">
-        <v>55</v>
-      </c>
-      <c r="D18" t="b">
-        <v>0</v>
+      <c r="B18">
+        <v>59</v>
+      </c>
+      <c r="C18" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" t="s">
+        <v>106</v>
       </c>
       <c r="E18">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
@@ -3820,64 +4159,64 @@
       <c r="J18" t="b">
         <v>0</v>
       </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
       <c r="L18" t="b">
         <v>0</v>
       </c>
-      <c r="M18">
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18">
         <v>2</v>
       </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18">
+      <c r="P18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q18">
         <v>80</v>
       </c>
-      <c r="P18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q18">
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18">
         <v>3</v>
       </c>
-      <c r="R18" t="b">
-        <v>0</v>
-      </c>
-      <c r="S18">
+      <c r="T18" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18">
         <v>2</v>
       </c>
-      <c r="T18" t="b">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>1</v>
-      </c>
       <c r="V18" t="b">
         <v>0</v>
       </c>
       <c r="W18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X18" t="b">
         <v>0</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="b">
         <v>0</v>
       </c>
-      <c r="AA18" t="s">
-        <v>127</v>
+      <c r="AA18">
+        <v>7</v>
       </c>
       <c r="AB18" t="b">
         <v>0</v>
       </c>
-      <c r="AD18">
-        <v>0</v>
-      </c>
-      <c r="AE18">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="b">
+      <c r="AC18" t="s">
+        <v>193</v>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18">
         <v>0</v>
       </c>
       <c r="AG18">
@@ -3887,39 +4226,42 @@
         <v>0</v>
       </c>
       <c r="AI18">
-        <v>1</v>
-      </c>
-      <c r="AJ18">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18">
         <v>0</v>
       </c>
       <c r="AL18">
-        <v>1</v>
-      </c>
-      <c r="AM18">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AM18" t="b">
+        <v>0</v>
       </c>
       <c r="AN18">
         <v>0</v>
       </c>
-      <c r="AO18" t="b">
+      <c r="AO18">
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1</v>
-      </c>
-      <c r="AQ18">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="b">
+        <v>0</v>
       </c>
       <c r="AR18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS18">
         <v>0</v>
       </c>
-      <c r="AU18" t="b">
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
         <v>0</v>
       </c>
       <c r="AW18" t="b">
@@ -3934,76 +4276,73 @@
       <c r="BC18" t="b">
         <v>0</v>
       </c>
-      <c r="BF18" t="b">
+      <c r="BE18" t="b">
         <v>0</v>
       </c>
       <c r="BH18" t="b">
         <v>0</v>
       </c>
-      <c r="BI18">
-        <v>3</v>
-      </c>
-      <c r="BJ18">
-        <v>0</v>
-      </c>
-      <c r="BK18" t="s">
-        <v>186</v>
+      <c r="BJ18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
       </c>
       <c r="BL18">
-        <v>1</v>
-      </c>
-      <c r="BM18" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BM18" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:65">
       <c r="A19" t="s">
         <v>82</v>
       </c>
-      <c r="B19" t="s">
-        <v>96</v>
-      </c>
-      <c r="C19">
-        <v>56</v>
-      </c>
-      <c r="D19" t="b">
-        <v>0</v>
+      <c r="B19">
+        <v>69</v>
+      </c>
+      <c r="C19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" t="s">
+        <v>106</v>
       </c>
       <c r="E19">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
       </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
-      <c r="M19">
-        <v>2</v>
-      </c>
       <c r="N19" t="b">
         <v>0</v>
       </c>
       <c r="O19">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
@@ -4015,7 +4354,7 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V19" t="b">
         <v>0</v>
@@ -4027,25 +4366,25 @@
         <v>0</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="b">
         <v>0</v>
       </c>
-      <c r="AA19" t="s">
-        <v>128</v>
+      <c r="AA19">
+        <v>11</v>
       </c>
       <c r="AB19" t="b">
         <v>0</v>
       </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="b">
-        <v>0</v>
+      <c r="AC19" t="s">
+        <v>194</v>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>1</v>
       </c>
       <c r="AG19">
         <v>1</v>
@@ -4056,37 +4395,40 @@
       <c r="AI19">
         <v>1</v>
       </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="b">
-        <v>0</v>
+      <c r="AJ19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>1</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
-      <c r="AM19">
+      <c r="AM19" t="b">
         <v>0</v>
       </c>
       <c r="AN19">
-        <v>1</v>
-      </c>
-      <c r="AO19" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>1</v>
       </c>
       <c r="AP19">
         <v>1</v>
       </c>
-      <c r="AQ19">
+      <c r="AQ19" t="b">
         <v>0</v>
       </c>
       <c r="AR19">
         <v>1</v>
       </c>
       <c r="AS19">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT19">
+        <v>1</v>
+      </c>
+      <c r="AU19">
         <v>0</v>
       </c>
       <c r="AW19" t="b">
@@ -4101,117 +4443,114 @@
       <c r="BC19" t="b">
         <v>0</v>
       </c>
-      <c r="BF19" t="b">
+      <c r="BE19" t="b">
         <v>0</v>
       </c>
       <c r="BH19" t="b">
         <v>0</v>
       </c>
-      <c r="BI19">
-        <v>2</v>
-      </c>
-      <c r="BJ19">
-        <v>0</v>
-      </c>
-      <c r="BK19" t="s">
-        <v>186</v>
+      <c r="BJ19" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>3</v>
       </c>
       <c r="BL19">
-        <v>4</v>
-      </c>
-      <c r="BM19" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BM19" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:65">
       <c r="A20" t="s">
         <v>83</v>
       </c>
-      <c r="B20" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20">
-        <v>56</v>
-      </c>
-      <c r="D20" t="b">
-        <v>0</v>
+      <c r="B20">
+        <v>54</v>
+      </c>
+      <c r="C20" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" t="s">
+        <v>105</v>
       </c>
       <c r="E20">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
       <c r="L20" t="b">
         <v>0</v>
       </c>
-      <c r="M20">
-        <v>4</v>
-      </c>
       <c r="N20" t="b">
         <v>0</v>
       </c>
       <c r="O20">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="P20" t="b">
         <v>0</v>
       </c>
       <c r="Q20">
+        <v>90</v>
+      </c>
+      <c r="R20" t="b">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>2</v>
+      </c>
+      <c r="T20" t="b">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA20">
         <v>5</v>
       </c>
-      <c r="R20" t="b">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>5</v>
-      </c>
-      <c r="T20" t="b">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>4</v>
-      </c>
-      <c r="V20" t="b">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>4</v>
-      </c>
-      <c r="X20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>18</v>
-      </c>
-      <c r="Z20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>129</v>
-      </c>
       <c r="AB20" t="b">
         <v>0</v>
       </c>
-      <c r="AD20">
-        <v>1</v>
-      </c>
-      <c r="AE20">
-        <v>1</v>
-      </c>
-      <c r="AF20" t="b">
+      <c r="AC20" t="s">
+        <v>188</v>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20">
         <v>0</v>
       </c>
       <c r="AG20">
@@ -4221,31 +4560,31 @@
         <v>0</v>
       </c>
       <c r="AI20">
-        <v>1</v>
-      </c>
-      <c r="AJ20">
-        <v>1</v>
-      </c>
-      <c r="AK20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL20">
-        <v>1</v>
-      </c>
-      <c r="AM20">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>225</v>
+      </c>
+      <c r="AM20" t="b">
+        <v>0</v>
       </c>
       <c r="AN20">
         <v>1</v>
       </c>
-      <c r="AO20" t="b">
+      <c r="AO20">
         <v>0</v>
       </c>
       <c r="AP20">
         <v>1</v>
       </c>
-      <c r="AQ20">
-        <v>1</v>
+      <c r="AQ20" t="b">
+        <v>0</v>
       </c>
       <c r="AR20">
         <v>1</v>
@@ -4253,7 +4592,10 @@
       <c r="AS20">
         <v>0</v>
       </c>
-      <c r="AU20" t="b">
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
         <v>0</v>
       </c>
       <c r="AW20" t="b">
@@ -4268,49 +4610,46 @@
       <c r="BC20" t="b">
         <v>0</v>
       </c>
-      <c r="BF20" t="b">
+      <c r="BE20" t="b">
         <v>0</v>
       </c>
       <c r="BH20" t="b">
         <v>0</v>
       </c>
-      <c r="BI20">
-        <v>5</v>
-      </c>
-      <c r="BJ20">
-        <v>0</v>
-      </c>
-      <c r="BK20" t="s">
-        <v>186</v>
+      <c r="BJ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK20">
+        <v>1</v>
       </c>
       <c r="BL20">
-        <v>7</v>
-      </c>
-      <c r="BM20" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BM20" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:65">
       <c r="A21" t="s">
         <v>84</v>
       </c>
-      <c r="B21" t="s">
-        <v>97</v>
-      </c>
-      <c r="C21">
-        <v>65</v>
-      </c>
-      <c r="D21" t="b">
-        <v>0</v>
+      <c r="B21">
+        <v>62</v>
+      </c>
+      <c r="C21" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" t="s">
+        <v>106</v>
       </c>
       <c r="E21">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -4321,106 +4660,109 @@
       <c r="J21" t="b">
         <v>0</v>
       </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
-      <c r="M21">
-        <v>2</v>
-      </c>
       <c r="N21" t="b">
         <v>0</v>
       </c>
       <c r="O21">
-        <v>85</v>
+        <v>3</v>
       </c>
       <c r="P21" t="b">
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
       </c>
       <c r="S21">
+        <v>4</v>
+      </c>
+      <c r="T21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>4</v>
+      </c>
+      <c r="V21" t="b">
+        <v>0</v>
+      </c>
+      <c r="W21">
         <v>3</v>
       </c>
-      <c r="T21" t="b">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>1</v>
-      </c>
-      <c r="V21" t="b">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>2</v>
-      </c>
       <c r="X21" t="b">
         <v>0</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z21" t="b">
         <v>0</v>
       </c>
-      <c r="AA21" t="s">
-        <v>130</v>
+      <c r="AA21">
+        <v>14</v>
       </c>
       <c r="AB21" t="b">
         <v>0</v>
       </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="b">
+      <c r="AC21" t="s">
+        <v>195</v>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21">
         <v>0</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH21" t="b">
         <v>0</v>
       </c>
       <c r="AI21">
-        <v>0</v>
-      </c>
-      <c r="AJ21">
-        <v>1</v>
-      </c>
-      <c r="AK21" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AJ21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>1</v>
       </c>
       <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AM21" t="b">
+        <v>0</v>
       </c>
       <c r="AN21">
         <v>1</v>
       </c>
-      <c r="AO21" t="b">
-        <v>0</v>
+      <c r="AO21">
+        <v>1</v>
       </c>
       <c r="AP21">
         <v>1</v>
       </c>
-      <c r="AQ21">
+      <c r="AQ21" t="b">
         <v>0</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
         <v>0</v>
       </c>
       <c r="AW21" t="b">
@@ -4435,381 +4777,357 @@
       <c r="BC21" t="b">
         <v>0</v>
       </c>
-      <c r="BF21" t="b">
+      <c r="BE21" t="b">
         <v>0</v>
       </c>
       <c r="BH21" t="b">
         <v>0</v>
       </c>
-      <c r="BI21">
-        <v>2</v>
-      </c>
-      <c r="BJ21">
-        <v>1</v>
-      </c>
-      <c r="BK21" t="s">
-        <v>189</v>
+      <c r="BJ21" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>5</v>
       </c>
       <c r="BL21">
-        <v>5</v>
-      </c>
-      <c r="BM21" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BM21" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="22" spans="1:65">
       <c r="A22" t="s">
         <v>85</v>
       </c>
-      <c r="B22" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22">
-        <v>65</v>
-      </c>
-      <c r="D22" t="b">
-        <v>0</v>
+      <c r="B22">
+        <v>60</v>
+      </c>
+      <c r="C22" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" t="s">
+        <v>106</v>
       </c>
       <c r="E22">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
       </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
-      <c r="M22">
+      <c r="N22" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22">
         <v>2</v>
       </c>
-      <c r="N22" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>70</v>
-      </c>
       <c r="P22" t="b">
         <v>0</v>
       </c>
       <c r="Q22">
+        <v>85</v>
+      </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>2</v>
+      </c>
+      <c r="T22" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>2</v>
+      </c>
+      <c r="V22" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>2</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>7</v>
+      </c>
+      <c r="AB22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>183</v>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>1</v>
+      </c>
+      <c r="AJ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>1</v>
+      </c>
+      <c r="AL22">
+        <v>1</v>
+      </c>
+      <c r="AM22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>1</v>
+      </c>
+      <c r="AP22">
+        <v>1</v>
+      </c>
+      <c r="AQ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>1</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK22">
         <v>4</v>
       </c>
-      <c r="R22" t="b">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>4</v>
-      </c>
-      <c r="T22" t="b">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>3</v>
-      </c>
-      <c r="V22" t="b">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>3</v>
-      </c>
-      <c r="X22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y22">
-        <v>14</v>
-      </c>
-      <c r="Z22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>131</v>
-      </c>
-      <c r="AB22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>1</v>
-      </c>
-      <c r="AE22">
-        <v>1</v>
-      </c>
-      <c r="AF22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI22">
-        <v>0</v>
-      </c>
-      <c r="AJ22">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL22">
-        <v>0</v>
-      </c>
-      <c r="AM22">
-        <v>1</v>
-      </c>
-      <c r="AN22">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP22">
-        <v>0</v>
-      </c>
-      <c r="AQ22">
-        <v>0</v>
-      </c>
-      <c r="AR22">
-        <v>1</v>
-      </c>
-      <c r="AS22">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="b">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC22" t="b">
-        <v>0</v>
-      </c>
-      <c r="BF22" t="b">
-        <v>0</v>
-      </c>
-      <c r="BH22" t="b">
-        <v>0</v>
-      </c>
-      <c r="BI22">
-        <v>1</v>
-      </c>
-      <c r="BJ22">
-        <v>1</v>
-      </c>
-      <c r="BK22" t="s">
-        <v>190</v>
-      </c>
       <c r="BL22">
-        <v>2</v>
-      </c>
-      <c r="BM22" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BM22" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:65">
       <c r="A23" t="s">
         <v>86</v>
       </c>
-      <c r="B23" t="s">
-        <v>97</v>
-      </c>
-      <c r="C23">
-        <v>77</v>
-      </c>
-      <c r="D23" t="b">
-        <v>1</v>
+      <c r="B23">
+        <v>65</v>
+      </c>
+      <c r="C23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" t="s">
+        <v>105</v>
       </c>
       <c r="E23">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23" t="s">
-        <v>98</v>
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>63</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
       </c>
-      <c r="I23" t="s">
-        <v>103</v>
+      <c r="I23">
+        <v>1</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
       </c>
-      <c r="K23" t="s">
-        <v>107</v>
+      <c r="K23">
+        <v>1</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
-      <c r="M23">
+      <c r="N23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23">
         <v>2</v>
       </c>
-      <c r="N23" t="b">
-        <v>1</v>
-      </c>
-      <c r="O23">
-        <v>80</v>
-      </c>
       <c r="P23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23">
+        <v>70</v>
+      </c>
+      <c r="R23" t="b">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>4</v>
+      </c>
+      <c r="T23" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>4</v>
+      </c>
+      <c r="V23" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23">
         <v>3</v>
       </c>
-      <c r="R23" t="b">
-        <v>1</v>
-      </c>
-      <c r="S23">
+      <c r="X23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y23">
         <v>3</v>
       </c>
-      <c r="T23" t="b">
-        <v>1</v>
-      </c>
-      <c r="U23">
-        <v>3</v>
-      </c>
-      <c r="V23" t="b">
-        <v>1</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y23">
-        <v>9</v>
-      </c>
       <c r="Z23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>132</v>
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>14</v>
       </c>
       <c r="AB23" t="b">
         <v>0</v>
       </c>
       <c r="AC23" t="s">
-        <v>142</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>147</v>
-      </c>
-      <c r="AE23" t="s">
-        <v>148</v>
-      </c>
-      <c r="AF23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>146</v>
+        <v>196</v>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>1</v>
+      </c>
+      <c r="AG23">
+        <v>1</v>
       </c>
       <c r="AH23" t="b">
         <v>0</v>
       </c>
-      <c r="AI23" t="s">
-        <v>154</v>
-      </c>
-      <c r="AJ23" t="s">
-        <v>146</v>
-      </c>
-      <c r="AK23" t="b">
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23">
         <v>0</v>
       </c>
       <c r="AL23" t="s">
-        <v>159</v>
-      </c>
-      <c r="AM23" t="s">
-        <v>146</v>
-      </c>
-      <c r="AN23" t="s">
-        <v>146</v>
-      </c>
-      <c r="AO23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="s">
-        <v>142</v>
-      </c>
-      <c r="AQ23" t="s">
-        <v>164</v>
-      </c>
-      <c r="AR23" t="s">
-        <v>165</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>98</v>
+        <v>225</v>
+      </c>
+      <c r="AM23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>1</v>
+      </c>
+      <c r="AP23">
+        <v>1</v>
+      </c>
+      <c r="AQ23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
       </c>
       <c r="AT23">
-        <v>1.325</v>
-      </c>
-      <c r="AU23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV23">
-        <v>150</v>
+        <v>1</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
       </c>
       <c r="AW23" t="b">
         <v>0</v>
       </c>
-      <c r="AX23">
-        <v>1.475</v>
-      </c>
       <c r="AY23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AZ23" t="s">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="b">
         <v>0</v>
       </c>
-      <c r="BB23" t="s">
-        <v>172</v>
-      </c>
       <c r="BC23" t="b">
         <v>0</v>
       </c>
-      <c r="BD23" t="s">
-        <v>143</v>
-      </c>
-      <c r="BE23" t="s">
-        <v>175</v>
-      </c>
-      <c r="BF23" t="b">
-        <v>1</v>
-      </c>
-      <c r="BG23" t="s">
-        <v>183</v>
+      <c r="BE23" t="b">
+        <v>0</v>
       </c>
       <c r="BH23" t="b">
         <v>0</v>
       </c>
+      <c r="BJ23" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>1</v>
+      </c>
       <c r="BL23">
-        <v>10</v>
-      </c>
-      <c r="BM23" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="BM23" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:65">
@@ -4819,185 +5137,185 @@
       <c r="B24" t="s">
         <v>97</v>
       </c>
-      <c r="C24">
-        <v>51</v>
-      </c>
-      <c r="D24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24">
-        <v>47</v>
+      <c r="C24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" t="s">
+        <v>108</v>
       </c>
       <c r="F24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
       </c>
-      <c r="M24">
-        <v>2</v>
+      <c r="M24" t="s">
+        <v>134</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
       </c>
-      <c r="O24">
-        <v>90</v>
+      <c r="O24" t="s">
+        <v>142</v>
       </c>
       <c r="P24" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q24">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>147</v>
       </c>
       <c r="R24" t="b">
-        <v>1</v>
-      </c>
-      <c r="S24">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="S24" t="s">
+        <v>153</v>
       </c>
       <c r="T24" t="b">
-        <v>1</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U24" t="s">
+        <v>162</v>
       </c>
       <c r="V24" t="b">
         <v>0</v>
       </c>
-      <c r="W24">
-        <v>0</v>
+      <c r="W24" t="s">
+        <v>168</v>
       </c>
       <c r="X24" t="b">
         <v>0</v>
       </c>
-      <c r="Y24">
-        <v>3</v>
+      <c r="Y24" t="s">
+        <v>172</v>
       </c>
       <c r="Z24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="s">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="AB24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="s">
-        <v>143</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>143</v>
+        <v>197</v>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
       </c>
       <c r="AE24" t="s">
-        <v>149</v>
-      </c>
-      <c r="AF24" t="b">
-        <v>1</v>
+        <v>207</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>212</v>
       </c>
       <c r="AG24" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="AH24" t="b">
         <v>0</v>
       </c>
       <c r="AI24" t="s">
-        <v>143</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>142</v>
-      </c>
-      <c r="AK24" t="b">
-        <v>1</v>
+        <v>211</v>
+      </c>
+      <c r="AJ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>221</v>
       </c>
       <c r="AL24" t="s">
-        <v>143</v>
-      </c>
-      <c r="AM24" t="s">
-        <v>160</v>
+        <v>211</v>
+      </c>
+      <c r="AM24" t="b">
+        <v>0</v>
       </c>
       <c r="AN24" t="s">
-        <v>159</v>
-      </c>
-      <c r="AO24" t="b">
-        <v>0</v>
+        <v>229</v>
+      </c>
+      <c r="AO24" t="s">
+        <v>227</v>
       </c>
       <c r="AP24" t="s">
-        <v>142</v>
-      </c>
-      <c r="AQ24" t="s">
-        <v>146</v>
+        <v>211</v>
+      </c>
+      <c r="AQ24" t="b">
+        <v>0</v>
       </c>
       <c r="AR24" t="s">
-        <v>143</v>
+        <v>236</v>
       </c>
       <c r="AS24" t="s">
-        <v>98</v>
-      </c>
-      <c r="AT24">
-        <v>300</v>
-      </c>
-      <c r="AU24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AV24">
-        <v>38</v>
+        <v>238</v>
+      </c>
+      <c r="AT24" t="s">
+        <v>239</v>
+      </c>
+      <c r="AU24" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>241</v>
       </c>
       <c r="AW24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AX24">
-        <v>338</v>
+        <v>0</v>
+      </c>
+      <c r="AX24" t="s">
+        <v>249</v>
       </c>
       <c r="AY24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="s">
-        <v>168</v>
+        <v>257</v>
       </c>
       <c r="BA24" t="b">
         <v>0</v>
       </c>
       <c r="BB24" t="s">
-        <v>146</v>
+        <v>265</v>
       </c>
       <c r="BC24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE24" t="s">
-        <v>176</v>
-      </c>
-      <c r="BF24" t="b">
-        <v>1</v>
+        <v>271</v>
+      </c>
+      <c r="BE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="s">
+        <v>208</v>
       </c>
       <c r="BG24" t="s">
-        <v>184</v>
+        <v>276</v>
       </c>
       <c r="BH24" t="b">
         <v>0</v>
       </c>
-      <c r="BL24">
-        <v>3</v>
-      </c>
-      <c r="BM24" t="b">
-        <v>1</v>
+      <c r="BI24" t="s">
+        <v>285</v>
+      </c>
+      <c r="BJ24" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:65">
@@ -5005,124 +5323,187 @@
         <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25">
-        <v>72</v>
-      </c>
-      <c r="D25" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25">
-        <v>62</v>
+        <v>98</v>
+      </c>
+      <c r="C25" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" t="s">
+        <v>109</v>
       </c>
       <c r="F25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="L25" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="M25" t="s">
+        <v>135</v>
       </c>
       <c r="N25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="P25" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q25">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>148</v>
       </c>
       <c r="R25" t="b">
-        <v>1</v>
-      </c>
-      <c r="S25">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="S25" t="s">
+        <v>154</v>
       </c>
       <c r="T25" t="b">
-        <v>1</v>
-      </c>
-      <c r="U25">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="U25" t="s">
+        <v>145</v>
       </c>
       <c r="V25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W25">
         <v>0</v>
       </c>
       <c r="X25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y25">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="AB25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="b">
-        <v>0</v>
+      <c r="AC25" t="s">
+        <v>198</v>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>208</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>215</v>
       </c>
       <c r="AH25" t="b">
         <v>0</v>
       </c>
-      <c r="AK25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="b">
-        <v>0</v>
+      <c r="AI25" t="s">
+        <v>208</v>
+      </c>
+      <c r="AJ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>226</v>
+      </c>
+      <c r="AM25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>208</v>
+      </c>
+      <c r="AO25" t="s">
+        <v>232</v>
+      </c>
+      <c r="AP25" t="s">
+        <v>229</v>
+      </c>
+      <c r="AQ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="s">
+        <v>224</v>
+      </c>
+      <c r="AS25" t="s">
+        <v>227</v>
+      </c>
+      <c r="AT25" t="s">
+        <v>213</v>
+      </c>
+      <c r="AU25" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV25" t="s">
+        <v>242</v>
       </c>
       <c r="AW25" t="b">
         <v>0</v>
       </c>
+      <c r="AX25" t="s">
+        <v>250</v>
+      </c>
       <c r="AY25" t="b">
         <v>0</v>
       </c>
+      <c r="AZ25" t="s">
+        <v>258</v>
+      </c>
       <c r="BA25" t="b">
         <v>0</v>
       </c>
+      <c r="BB25" t="s">
+        <v>266</v>
+      </c>
       <c r="BC25" t="b">
         <v>0</v>
       </c>
-      <c r="BF25" t="b">
-        <v>0</v>
+      <c r="BD25" t="s">
+        <v>272</v>
+      </c>
+      <c r="BE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="s">
+        <v>124</v>
+      </c>
+      <c r="BG25" t="s">
+        <v>277</v>
       </c>
       <c r="BH25" t="b">
         <v>0</v>
       </c>
-      <c r="BL25">
-        <v>10</v>
-      </c>
-      <c r="BM25" t="b">
-        <v>1</v>
+      <c r="BI25" t="s">
+        <v>286</v>
+      </c>
+      <c r="BJ25" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:65">
@@ -5130,186 +5511,123 @@
         <v>89</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26">
-        <v>62</v>
-      </c>
-      <c r="D26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26">
-        <v>51</v>
+        <v>99</v>
+      </c>
+      <c r="C26" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" t="s">
+        <v>108</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="H26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="L26" t="b">
-        <v>1</v>
-      </c>
-      <c r="M26">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="M26" t="s">
+        <v>136</v>
       </c>
       <c r="N26" t="b">
-        <v>1</v>
-      </c>
-      <c r="O26">
-        <v>90</v>
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
+        <v>143</v>
       </c>
       <c r="P26" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q26">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>149</v>
       </c>
       <c r="R26" t="b">
-        <v>1</v>
-      </c>
-      <c r="S26">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="S26" t="s">
+        <v>155</v>
       </c>
       <c r="T26" t="b">
-        <v>1</v>
-      </c>
-      <c r="U26">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="U26" t="s">
+        <v>163</v>
       </c>
       <c r="V26" t="b">
-        <v>1</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W26" t="s">
+        <v>168</v>
       </c>
       <c r="X26" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y26">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>172</v>
       </c>
       <c r="Z26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="AB26" t="b">
         <v>0</v>
       </c>
       <c r="AC26" t="s">
-        <v>144</v>
-      </c>
-      <c r="AD26" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE26" t="s">
-        <v>143</v>
-      </c>
-      <c r="AF26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>143</v>
+        <v>199</v>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
       </c>
       <c r="AH26" t="b">
         <v>0</v>
       </c>
-      <c r="AI26" t="s">
-        <v>155</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>142</v>
-      </c>
-      <c r="AK26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="s">
-        <v>146</v>
-      </c>
-      <c r="AM26" t="s">
-        <v>146</v>
-      </c>
-      <c r="AN26" t="s">
-        <v>142</v>
-      </c>
-      <c r="AO26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="s">
-        <v>142</v>
-      </c>
-      <c r="AQ26" t="s">
-        <v>142</v>
-      </c>
-      <c r="AR26" t="s">
-        <v>143</v>
-      </c>
-      <c r="AS26" t="s">
-        <v>98</v>
-      </c>
-      <c r="AT26">
-        <v>1.063</v>
-      </c>
-      <c r="AU26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV26">
-        <v>75</v>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="b">
+        <v>0</v>
       </c>
       <c r="AW26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AX26">
-        <v>1.138</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AZ26" t="s">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="b">
         <v>0</v>
       </c>
-      <c r="BB26" t="s">
-        <v>146</v>
-      </c>
       <c r="BC26" t="b">
         <v>0</v>
       </c>
-      <c r="BD26" t="s">
-        <v>143</v>
-      </c>
-      <c r="BE26" t="s">
-        <v>177</v>
-      </c>
-      <c r="BF26" t="b">
-        <v>1</v>
-      </c>
-      <c r="BG26" t="s">
-        <v>183</v>
+      <c r="BE26" t="b">
+        <v>0</v>
       </c>
       <c r="BH26" t="b">
-        <v>1</v>
-      </c>
-      <c r="BL26">
-        <v>11</v>
-      </c>
-      <c r="BM26" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5318,187 +5636,187 @@
         <v>90</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27">
-        <v>62</v>
-      </c>
-      <c r="D27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27">
-        <v>61</v>
+        <v>100</v>
+      </c>
+      <c r="C27" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" t="s">
+        <v>107</v>
+      </c>
+      <c r="E27" t="s">
+        <v>110</v>
       </c>
       <c r="F27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
       </c>
-      <c r="M27">
-        <v>1</v>
+      <c r="M27" t="s">
+        <v>137</v>
       </c>
       <c r="N27" t="b">
-        <v>1</v>
-      </c>
-      <c r="O27">
-        <v>90</v>
+        <v>0</v>
+      </c>
+      <c r="O27" t="s">
+        <v>144</v>
       </c>
       <c r="P27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q27">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>150</v>
       </c>
       <c r="R27" t="b">
-        <v>1</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="S27" t="s">
+        <v>156</v>
       </c>
       <c r="T27" t="b">
-        <v>1</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U27" t="s">
+        <v>164</v>
       </c>
       <c r="V27" t="b">
         <v>0</v>
       </c>
-      <c r="W27">
-        <v>0</v>
+      <c r="W27" t="s">
+        <v>169</v>
       </c>
       <c r="X27" t="b">
         <v>0</v>
       </c>
-      <c r="Y27">
-        <v>1</v>
+      <c r="Y27" t="s">
+        <v>173</v>
       </c>
       <c r="Z27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="s">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="AB27" t="b">
         <v>0</v>
       </c>
       <c r="AC27" t="s">
-        <v>145</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>143</v>
+        <v>200</v>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
       </c>
       <c r="AE27" t="s">
-        <v>143</v>
-      </c>
-      <c r="AF27" t="b">
-        <v>0</v>
+        <v>209</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>213</v>
       </c>
       <c r="AG27" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="AH27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="s">
-        <v>143</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>146</v>
-      </c>
-      <c r="AK27" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="AJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>222</v>
       </c>
       <c r="AL27" t="s">
-        <v>143</v>
-      </c>
-      <c r="AM27" t="s">
-        <v>143</v>
+        <v>224</v>
+      </c>
+      <c r="AM27" t="b">
+        <v>0</v>
       </c>
       <c r="AN27" t="s">
-        <v>142</v>
-      </c>
-      <c r="AO27" t="b">
-        <v>0</v>
+        <v>211</v>
+      </c>
+      <c r="AO27" t="s">
+        <v>227</v>
       </c>
       <c r="AP27" t="s">
-        <v>142</v>
-      </c>
-      <c r="AQ27" t="s">
-        <v>143</v>
+        <v>230</v>
+      </c>
+      <c r="AQ27" t="b">
+        <v>0</v>
       </c>
       <c r="AR27" t="s">
-        <v>165</v>
+        <v>236</v>
       </c>
       <c r="AS27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AT27">
-        <v>300</v>
-      </c>
-      <c r="AU27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV27">
-        <v>0</v>
+        <v>224</v>
+      </c>
+      <c r="AT27" t="s">
+        <v>213</v>
+      </c>
+      <c r="AU27" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV27" t="s">
+        <v>243</v>
       </c>
       <c r="AW27" t="b">
         <v>0</v>
       </c>
-      <c r="AX27">
-        <v>300</v>
+      <c r="AX27" t="s">
+        <v>251</v>
       </c>
       <c r="AY27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="s">
-        <v>170</v>
+        <v>259</v>
       </c>
       <c r="BA27" t="b">
         <v>0</v>
       </c>
       <c r="BB27" t="s">
-        <v>173</v>
+        <v>267</v>
       </c>
       <c r="BC27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE27" t="s">
-        <v>178</v>
-      </c>
-      <c r="BF27" t="b">
-        <v>1</v>
+        <v>227</v>
+      </c>
+      <c r="BE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="s">
+        <v>208</v>
       </c>
       <c r="BG27" t="s">
-        <v>184</v>
+        <v>278</v>
       </c>
       <c r="BH27" t="b">
         <v>0</v>
       </c>
-      <c r="BL27">
-        <v>1</v>
-      </c>
-      <c r="BM27" t="b">
-        <v>1</v>
+      <c r="BI27" t="s">
+        <v>287</v>
+      </c>
+      <c r="BJ27" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:65">
@@ -5506,64 +5824,64 @@
         <v>91</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
-      </c>
-      <c r="C28">
-        <v>52</v>
-      </c>
-      <c r="D28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>51</v>
+        <v>100</v>
+      </c>
+      <c r="C28" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28" t="s">
+        <v>111</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
       </c>
-      <c r="M28">
-        <v>1</v>
+      <c r="M28" t="s">
+        <v>138</v>
       </c>
       <c r="N28" t="b">
-        <v>1</v>
-      </c>
-      <c r="O28">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="O28" t="s">
+        <v>145</v>
       </c>
       <c r="P28" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q28">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>148</v>
       </c>
       <c r="R28" t="b">
-        <v>1</v>
-      </c>
-      <c r="S28">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="S28" t="s">
+        <v>157</v>
       </c>
       <c r="T28" t="b">
-        <v>1</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U28" t="s">
+        <v>165</v>
       </c>
       <c r="V28" t="b">
         <v>0</v>
@@ -5575,118 +5893,118 @@
         <v>0</v>
       </c>
       <c r="Y28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="AB28" t="b">
         <v>0</v>
       </c>
       <c r="AC28" t="s">
-        <v>142</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>143</v>
+        <v>201</v>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
       </c>
       <c r="AE28" t="s">
-        <v>150</v>
-      </c>
-      <c r="AF28" t="b">
-        <v>0</v>
+        <v>210</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>213</v>
       </c>
       <c r="AG28" t="s">
-        <v>143</v>
+        <v>208</v>
       </c>
       <c r="AH28" t="b">
         <v>0</v>
       </c>
       <c r="AI28" t="s">
-        <v>143</v>
-      </c>
-      <c r="AJ28" t="s">
-        <v>143</v>
-      </c>
-      <c r="AK28" t="b">
-        <v>1</v>
+        <v>220</v>
+      </c>
+      <c r="AJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>213</v>
       </c>
       <c r="AL28" t="s">
-        <v>143</v>
-      </c>
-      <c r="AM28" t="s">
-        <v>146</v>
+        <v>227</v>
+      </c>
+      <c r="AM28" t="b">
+        <v>0</v>
       </c>
       <c r="AN28" t="s">
-        <v>146</v>
-      </c>
-      <c r="AO28" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="AO28" t="s">
+        <v>213</v>
       </c>
       <c r="AP28" t="s">
-        <v>146</v>
-      </c>
-      <c r="AQ28" t="s">
-        <v>146</v>
+        <v>224</v>
+      </c>
+      <c r="AQ28" t="b">
+        <v>0</v>
       </c>
       <c r="AR28" t="s">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="AS28" t="s">
-        <v>98</v>
-      </c>
-      <c r="AT28">
-        <v>150</v>
-      </c>
-      <c r="AU28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV28">
-        <v>150</v>
+        <v>213</v>
+      </c>
+      <c r="AT28" t="s">
+        <v>239</v>
+      </c>
+      <c r="AU28" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV28" t="s">
+        <v>244</v>
       </c>
       <c r="AW28" t="b">
         <v>0</v>
       </c>
-      <c r="AX28">
-        <v>300</v>
+      <c r="AX28" t="s">
+        <v>252</v>
       </c>
       <c r="AY28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="s">
-        <v>167</v>
+        <v>244</v>
       </c>
       <c r="BA28" t="b">
         <v>0</v>
       </c>
       <c r="BB28" t="s">
-        <v>173</v>
+        <v>268</v>
       </c>
       <c r="BC28" t="b">
         <v>0</v>
       </c>
       <c r="BD28" t="s">
-        <v>143</v>
-      </c>
-      <c r="BE28" t="s">
-        <v>179</v>
-      </c>
-      <c r="BF28" t="b">
-        <v>1</v>
+        <v>273</v>
+      </c>
+      <c r="BE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="s">
+        <v>124</v>
       </c>
       <c r="BG28" t="s">
-        <v>183</v>
+        <v>279</v>
       </c>
       <c r="BH28" t="b">
         <v>0</v>
       </c>
-      <c r="BL28">
-        <v>2.2</v>
-      </c>
-      <c r="BM28" t="b">
-        <v>1</v>
+      <c r="BI28" t="s">
+        <v>286</v>
+      </c>
+      <c r="BJ28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:65">
@@ -5694,64 +6012,64 @@
         <v>92</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29">
-        <v>65</v>
-      </c>
-      <c r="D29" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29">
-        <v>57</v>
+        <v>101</v>
+      </c>
+      <c r="C29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" t="s">
+        <v>106</v>
+      </c>
+      <c r="E29" t="s">
+        <v>112</v>
       </c>
       <c r="F29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
       </c>
-      <c r="M29">
-        <v>2</v>
+      <c r="M29" t="s">
+        <v>134</v>
       </c>
       <c r="N29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O29">
-        <v>90</v>
+        <v>0</v>
+      </c>
+      <c r="O29" t="s">
+        <v>145</v>
       </c>
       <c r="P29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q29">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>151</v>
       </c>
       <c r="R29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S29">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="S29" t="s">
+        <v>158</v>
       </c>
       <c r="T29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U29">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U29" t="s">
+        <v>166</v>
       </c>
       <c r="V29" t="b">
         <v>0</v>
@@ -5763,117 +6081,117 @@
         <v>0</v>
       </c>
       <c r="Y29">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AB29" t="b">
         <v>0</v>
       </c>
       <c r="AC29" t="s">
-        <v>143</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>143</v>
+        <v>202</v>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
       </c>
       <c r="AE29" t="s">
-        <v>151</v>
-      </c>
-      <c r="AF29" t="b">
-        <v>0</v>
+        <v>207</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>213</v>
       </c>
       <c r="AG29" t="s">
-        <v>146</v>
+        <v>217</v>
       </c>
       <c r="AH29" t="b">
         <v>0</v>
       </c>
       <c r="AI29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AJ29" t="s">
-        <v>157</v>
-      </c>
-      <c r="AK29" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="AJ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>213</v>
       </c>
       <c r="AL29" t="s">
-        <v>142</v>
-      </c>
-      <c r="AM29" t="s">
-        <v>146</v>
+        <v>216</v>
+      </c>
+      <c r="AM29" t="b">
+        <v>0</v>
       </c>
       <c r="AN29" t="s">
-        <v>161</v>
-      </c>
-      <c r="AO29" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="AO29" t="s">
+        <v>227</v>
       </c>
       <c r="AP29" t="s">
-        <v>142</v>
-      </c>
-      <c r="AQ29" t="s">
-        <v>146</v>
+        <v>211</v>
+      </c>
+      <c r="AQ29" t="b">
+        <v>0</v>
       </c>
       <c r="AR29" t="s">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="AS29" t="s">
-        <v>98</v>
-      </c>
-      <c r="AT29">
-        <v>800</v>
-      </c>
-      <c r="AU29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AV29">
-        <v>0</v>
+        <v>227</v>
+      </c>
+      <c r="AT29" t="s">
+        <v>239</v>
+      </c>
+      <c r="AU29" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV29" t="s">
+        <v>245</v>
       </c>
       <c r="AW29" t="b">
         <v>0</v>
       </c>
-      <c r="AX29">
-        <v>900</v>
+      <c r="AX29" t="s">
+        <v>253</v>
       </c>
       <c r="AY29" t="b">
         <v>0</v>
       </c>
       <c r="AZ29" t="s">
-        <v>168</v>
+        <v>260</v>
       </c>
       <c r="BA29" t="b">
         <v>0</v>
       </c>
       <c r="BB29" t="s">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="BC29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE29" t="s">
-        <v>180</v>
-      </c>
-      <c r="BF29" t="b">
-        <v>1</v>
+        <v>274</v>
+      </c>
+      <c r="BE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="s">
+        <v>208</v>
       </c>
       <c r="BG29" t="s">
-        <v>184</v>
+        <v>280</v>
       </c>
       <c r="BH29" t="b">
         <v>0</v>
       </c>
-      <c r="BL29">
-        <v>6</v>
-      </c>
-      <c r="BM29" t="b">
+      <c r="BI29" t="s">
+        <v>285</v>
+      </c>
+      <c r="BJ29" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5882,186 +6200,186 @@
         <v>93</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
-      </c>
-      <c r="C30">
-        <v>65</v>
-      </c>
-      <c r="D30" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30">
-        <v>56</v>
+        <v>102</v>
+      </c>
+      <c r="C30" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" t="s">
+        <v>113</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
       </c>
-      <c r="M30">
-        <v>3</v>
+      <c r="M30" t="s">
+        <v>138</v>
       </c>
       <c r="N30" t="b">
-        <v>1</v>
-      </c>
-      <c r="O30">
-        <v>80</v>
+        <v>0</v>
+      </c>
+      <c r="O30" t="s">
+        <v>142</v>
       </c>
       <c r="P30" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q30">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>148</v>
       </c>
       <c r="R30" t="b">
-        <v>1</v>
-      </c>
-      <c r="S30">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="S30" t="s">
+        <v>154</v>
       </c>
       <c r="T30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U30">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="U30" t="s">
+        <v>142</v>
       </c>
       <c r="V30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="AB30" t="b">
         <v>0</v>
       </c>
       <c r="AC30" t="s">
-        <v>143</v>
-      </c>
-      <c r="AD30" t="s">
-        <v>143</v>
+        <v>203</v>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
       </c>
       <c r="AE30" t="s">
-        <v>152</v>
-      </c>
-      <c r="AF30" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>208</v>
       </c>
       <c r="AG30" t="s">
-        <v>146</v>
+        <v>218</v>
       </c>
       <c r="AH30" t="b">
         <v>0</v>
       </c>
       <c r="AI30" t="s">
-        <v>142</v>
-      </c>
-      <c r="AJ30" t="s">
-        <v>142</v>
-      </c>
-      <c r="AK30" t="b">
-        <v>0</v>
+        <v>211</v>
+      </c>
+      <c r="AJ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>223</v>
       </c>
       <c r="AL30" t="s">
-        <v>153</v>
-      </c>
-      <c r="AM30" t="s">
-        <v>146</v>
+        <v>228</v>
+      </c>
+      <c r="AM30" t="b">
+        <v>0</v>
       </c>
       <c r="AN30" t="s">
-        <v>162</v>
-      </c>
-      <c r="AO30" t="b">
-        <v>1</v>
+        <v>230</v>
+      </c>
+      <c r="AO30" t="s">
+        <v>227</v>
       </c>
       <c r="AP30" t="s">
-        <v>142</v>
-      </c>
-      <c r="AQ30" t="s">
-        <v>143</v>
+        <v>234</v>
+      </c>
+      <c r="AQ30" t="b">
+        <v>0</v>
       </c>
       <c r="AR30" t="s">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="AS30" t="s">
-        <v>166</v>
-      </c>
-      <c r="AT30">
-        <v>1.25</v>
-      </c>
-      <c r="AU30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV30">
-        <v>400</v>
+        <v>227</v>
+      </c>
+      <c r="AT30" t="s">
+        <v>239</v>
+      </c>
+      <c r="AU30" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV30" t="s">
+        <v>246</v>
       </c>
       <c r="AW30" t="b">
         <v>0</v>
       </c>
-      <c r="AX30">
-        <v>1.65</v>
+      <c r="AX30" t="s">
+        <v>252</v>
       </c>
       <c r="AY30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="s">
-        <v>170</v>
+        <v>261</v>
       </c>
       <c r="BA30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="s">
-        <v>174</v>
+        <v>266</v>
       </c>
       <c r="BC30" t="b">
         <v>0</v>
       </c>
       <c r="BD30" t="s">
-        <v>142</v>
-      </c>
-      <c r="BE30" t="s">
-        <v>181</v>
-      </c>
-      <c r="BF30" t="b">
-        <v>1</v>
+        <v>273</v>
+      </c>
+      <c r="BE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="s">
+        <v>124</v>
       </c>
       <c r="BG30" t="s">
-        <v>184</v>
+        <v>281</v>
       </c>
       <c r="BH30" t="b">
         <v>0</v>
       </c>
-      <c r="BL30">
-        <v>8</v>
-      </c>
-      <c r="BM30" t="b">
+      <c r="BI30" t="s">
+        <v>286</v>
+      </c>
+      <c r="BJ30" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6070,187 +6388,187 @@
         <v>94</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31">
-        <v>47</v>
-      </c>
-      <c r="D31" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31">
-        <v>44</v>
+        <v>102</v>
+      </c>
+      <c r="C31" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31" t="s">
+        <v>106</v>
+      </c>
+      <c r="E31" t="s">
+        <v>114</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
       </c>
-      <c r="M31">
-        <v>2</v>
+      <c r="M31" t="s">
+        <v>139</v>
       </c>
       <c r="N31" t="b">
-        <v>1</v>
-      </c>
-      <c r="O31">
-        <v>90</v>
+        <v>0</v>
+      </c>
+      <c r="O31" t="s">
+        <v>146</v>
       </c>
       <c r="P31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>152</v>
       </c>
       <c r="R31" t="b">
-        <v>1</v>
-      </c>
-      <c r="S31">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="S31" t="s">
+        <v>159</v>
       </c>
       <c r="T31" t="b">
-        <v>1</v>
-      </c>
-      <c r="U31">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="U31" t="s">
+        <v>146</v>
       </c>
       <c r="V31" t="b">
-        <v>1</v>
-      </c>
-      <c r="W31">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="W31" t="s">
+        <v>170</v>
       </c>
       <c r="X31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y31">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>145</v>
       </c>
       <c r="Z31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="AB31" t="b">
         <v>0</v>
       </c>
       <c r="AC31" t="s">
-        <v>142</v>
-      </c>
-      <c r="AD31" t="s">
-        <v>143</v>
+        <v>204</v>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
       </c>
       <c r="AE31" t="s">
-        <v>146</v>
-      </c>
-      <c r="AF31" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>213</v>
       </c>
       <c r="AG31" t="s">
-        <v>146</v>
+        <v>219</v>
       </c>
       <c r="AH31" t="b">
         <v>0</v>
       </c>
       <c r="AI31" t="s">
-        <v>143</v>
-      </c>
-      <c r="AJ31" t="s">
-        <v>158</v>
-      </c>
-      <c r="AK31" t="b">
-        <v>0</v>
+        <v>211</v>
+      </c>
+      <c r="AJ31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>224</v>
       </c>
       <c r="AL31" t="s">
-        <v>159</v>
-      </c>
-      <c r="AM31" t="s">
-        <v>146</v>
+        <v>224</v>
+      </c>
+      <c r="AM31" t="b">
+        <v>0</v>
       </c>
       <c r="AN31" t="s">
-        <v>146</v>
-      </c>
-      <c r="AO31" t="b">
-        <v>0</v>
+        <v>231</v>
+      </c>
+      <c r="AO31" t="s">
+        <v>227</v>
       </c>
       <c r="AP31" t="s">
-        <v>163</v>
-      </c>
-      <c r="AQ31" t="s">
-        <v>159</v>
+        <v>235</v>
+      </c>
+      <c r="AQ31" t="b">
+        <v>0</v>
       </c>
       <c r="AR31" t="s">
-        <v>146</v>
+        <v>224</v>
       </c>
       <c r="AS31" t="s">
-        <v>98</v>
-      </c>
-      <c r="AT31">
-        <v>1</v>
-      </c>
-      <c r="AU31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AV31">
-        <v>225</v>
+        <v>213</v>
+      </c>
+      <c r="AT31" t="s">
+        <v>239</v>
+      </c>
+      <c r="AU31" t="s">
+        <v>240</v>
+      </c>
+      <c r="AV31" t="s">
+        <v>247</v>
       </c>
       <c r="AW31" t="b">
         <v>0</v>
       </c>
-      <c r="AX31">
-        <v>1.225</v>
+      <c r="AX31" t="s">
+        <v>254</v>
       </c>
       <c r="AY31" t="b">
         <v>0</v>
       </c>
       <c r="AZ31" t="s">
-        <v>146</v>
+        <v>262</v>
       </c>
       <c r="BA31" t="b">
         <v>0</v>
       </c>
       <c r="BB31" t="s">
-        <v>172</v>
+        <v>269</v>
       </c>
       <c r="BC31" t="b">
         <v>0</v>
       </c>
       <c r="BD31" t="s">
-        <v>143</v>
-      </c>
-      <c r="BE31" t="s">
-        <v>175</v>
-      </c>
-      <c r="BF31" t="b">
-        <v>0</v>
+        <v>275</v>
+      </c>
+      <c r="BE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="s">
+        <v>230</v>
       </c>
       <c r="BG31" t="s">
-        <v>183</v>
+        <v>282</v>
       </c>
       <c r="BH31" t="b">
         <v>0</v>
       </c>
-      <c r="BL31">
-        <v>3.3</v>
-      </c>
-      <c r="BM31" t="b">
-        <v>1</v>
+      <c r="BI31" t="s">
+        <v>286</v>
+      </c>
+      <c r="BJ31" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:65">
@@ -6258,187 +6576,375 @@
         <v>95</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32">
-        <v>68</v>
-      </c>
-      <c r="D32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32">
-        <v>62</v>
+        <v>103</v>
+      </c>
+      <c r="C32" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" t="s">
+        <v>105</v>
+      </c>
+      <c r="E32" t="s">
+        <v>115</v>
       </c>
       <c r="F32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
       </c>
-      <c r="M32">
+      <c r="M32" t="s">
+        <v>140</v>
+      </c>
+      <c r="N32" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" t="s">
+        <v>142</v>
+      </c>
+      <c r="P32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>148</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32" t="s">
+        <v>160</v>
+      </c>
+      <c r="T32" t="b">
+        <v>0</v>
+      </c>
+      <c r="U32" t="s">
+        <v>167</v>
+      </c>
+      <c r="V32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W32" t="s">
+        <v>171</v>
+      </c>
+      <c r="X32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>174</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>205</v>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>208</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>211</v>
+      </c>
+      <c r="AH32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>211</v>
+      </c>
+      <c r="AJ32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>213</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>225</v>
+      </c>
+      <c r="AM32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO32" t="s">
+        <v>227</v>
+      </c>
+      <c r="AP32" t="s">
+        <v>211</v>
+      </c>
+      <c r="AQ32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="s">
+        <v>237</v>
+      </c>
+      <c r="AS32" t="s">
+        <v>233</v>
+      </c>
+      <c r="AT32" t="s">
+        <v>227</v>
+      </c>
+      <c r="AU32" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV32" t="s">
+        <v>248</v>
+      </c>
+      <c r="AW32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="s">
+        <v>255</v>
+      </c>
+      <c r="AY32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="s">
+        <v>263</v>
+      </c>
+      <c r="BA32" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="s">
+        <v>211</v>
+      </c>
+      <c r="BC32" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="s">
+        <v>271</v>
+      </c>
+      <c r="BE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="s">
+        <v>208</v>
+      </c>
+      <c r="BG32" t="s">
+        <v>283</v>
+      </c>
+      <c r="BH32" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI32" t="s">
+        <v>285</v>
+      </c>
+      <c r="BJ32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:62">
+      <c r="A33" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" t="s">
+        <v>116</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" t="s">
+        <v>100</v>
+      </c>
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="s">
+        <v>124</v>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>129</v>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" t="s">
+        <v>141</v>
+      </c>
+      <c r="N33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O33">
         <v>3</v>
       </c>
-      <c r="N32" t="b">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>80</v>
-      </c>
-      <c r="P32" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q32">
+      <c r="P33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>152</v>
+      </c>
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
+      <c r="S33" t="s">
+        <v>161</v>
+      </c>
+      <c r="T33" t="b">
+        <v>0</v>
+      </c>
+      <c r="U33">
         <v>3</v>
       </c>
-      <c r="R32" t="b">
-        <v>1</v>
-      </c>
-      <c r="S32">
-        <v>3</v>
-      </c>
-      <c r="T32" t="b">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>2</v>
-      </c>
-      <c r="X32" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y32">
+      <c r="V33" t="b">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA33">
         <v>8</v>
       </c>
-      <c r="Z32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>141</v>
-      </c>
-      <c r="AB32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="s">
-        <v>146</v>
-      </c>
-      <c r="AD32" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE32" t="s">
-        <v>143</v>
-      </c>
-      <c r="AF32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>146</v>
-      </c>
-      <c r="AH32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="s">
-        <v>146</v>
-      </c>
-      <c r="AJ32" t="s">
-        <v>142</v>
-      </c>
-      <c r="AK32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="s">
-        <v>143</v>
-      </c>
-      <c r="AM32" t="s">
-        <v>159</v>
-      </c>
-      <c r="AN32" t="s">
-        <v>146</v>
-      </c>
-      <c r="AO32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="s">
-        <v>142</v>
-      </c>
-      <c r="AQ32" t="s">
-        <v>142</v>
-      </c>
-      <c r="AR32" t="s">
-        <v>143</v>
-      </c>
-      <c r="AS32" t="s">
-        <v>98</v>
-      </c>
-      <c r="AT32">
-        <v>800</v>
-      </c>
-      <c r="AU32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AV32">
-        <v>25</v>
-      </c>
-      <c r="AW32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AX32">
-        <v>925</v>
-      </c>
-      <c r="AY32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AZ32" t="s">
-        <v>171</v>
-      </c>
-      <c r="BA32" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="s">
-        <v>143</v>
-      </c>
-      <c r="BC32" t="b">
-        <v>0</v>
-      </c>
-      <c r="BD32" t="s">
-        <v>142</v>
-      </c>
-      <c r="BE32" t="s">
-        <v>182</v>
-      </c>
-      <c r="BF32" t="b">
-        <v>0</v>
-      </c>
-      <c r="BG32" t="s">
-        <v>185</v>
-      </c>
-      <c r="BH32" t="b">
-        <v>0</v>
-      </c>
-      <c r="BL32">
-        <v>6</v>
-      </c>
-      <c r="BM32" t="b">
-        <v>1</v>
+      <c r="AB33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>206</v>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>211</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>208</v>
+      </c>
+      <c r="AG33" t="s">
+        <v>208</v>
+      </c>
+      <c r="AH33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>211</v>
+      </c>
+      <c r="AJ33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>211</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>207</v>
+      </c>
+      <c r="AM33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>208</v>
+      </c>
+      <c r="AO33" t="s">
+        <v>233</v>
+      </c>
+      <c r="AP33" t="s">
+        <v>211</v>
+      </c>
+      <c r="AQ33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="s">
+        <v>224</v>
+      </c>
+      <c r="AS33" t="s">
+        <v>224</v>
+      </c>
+      <c r="AT33" t="s">
+        <v>213</v>
+      </c>
+      <c r="AU33" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV33" t="s">
+        <v>246</v>
+      </c>
+      <c r="AW33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="s">
+        <v>256</v>
+      </c>
+      <c r="AY33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="s">
+        <v>264</v>
+      </c>
+      <c r="BA33" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="s">
+        <v>270</v>
+      </c>
+      <c r="BC33" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="s">
+        <v>213</v>
+      </c>
+      <c r="BE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="s">
+        <v>230</v>
+      </c>
+      <c r="BG33" t="s">
+        <v>284</v>
+      </c>
+      <c r="BH33" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI33" t="s">
+        <v>288</v>
+      </c>
+      <c r="BJ33" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
